--- a/data_lake/fixed_income/South Korea/SwapRate.xlsx
+++ b/data_lake/fixed_income/South Korea/SwapRate.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\fixed_income\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C095AC-42D6-4906-B025-C2BB88C3CBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E2FC7B-DB8F-450E-9ECC-8B1985D0C686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C9C890FF-C3F2-4A9F-8865-0BB25D5A743B}"/>
   </bookViews>
   <sheets>
     <sheet name="KR" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="27">
   <si>
     <t>https://www.kmbco.com/kor/rate/deri_rate.do#article1</t>
   </si>
@@ -219,7 +220,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -241,6 +242,7 @@
     </xf>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -558,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4AAE20-6E9C-4CCD-99FF-CD3680691C67}">
-  <dimension ref="A1:R763"/>
+  <dimension ref="A1:R772"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="4" bestFit="1" customWidth="1"/>
@@ -43298,6 +43300,510 @@
         <v>3.49</v>
       </c>
     </row>
+    <row r="764" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A764" s="4">
+        <v>46223</v>
+      </c>
+      <c r="B764" s="4">
+        <v>46223</v>
+      </c>
+      <c r="C764" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D764" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E764" s="2">
+        <v>3.4375</v>
+      </c>
+      <c r="F764" s="2">
+        <v>3.82</v>
+      </c>
+      <c r="G764" s="2">
+        <v>3.9550000000000001</v>
+      </c>
+      <c r="H764" s="2">
+        <v>4.0250000000000004</v>
+      </c>
+      <c r="I764" s="2">
+        <v>4.0750000000000002</v>
+      </c>
+      <c r="J764" s="2">
+        <v>4.13</v>
+      </c>
+      <c r="K764" s="2">
+        <v>4.1725000000000003</v>
+      </c>
+      <c r="L764" s="9">
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="M764" s="9">
+        <v>3.26</v>
+      </c>
+      <c r="N764" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="O764" s="9">
+        <v>3.52</v>
+      </c>
+      <c r="P764" s="9">
+        <v>3.57</v>
+      </c>
+      <c r="Q764" s="9">
+        <v>3.61</v>
+      </c>
+      <c r="R764" s="9">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="765" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A765" s="4">
+        <v>46224</v>
+      </c>
+      <c r="B765" s="4">
+        <v>46224</v>
+      </c>
+      <c r="C765" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D765" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E765" s="2">
+        <v>3.42</v>
+      </c>
+      <c r="F765" s="2">
+        <v>3.77</v>
+      </c>
+      <c r="G765" s="2">
+        <v>3.91</v>
+      </c>
+      <c r="H765" s="2">
+        <v>3.9824999999999999</v>
+      </c>
+      <c r="I765" s="2">
+        <v>4.0324999999999998</v>
+      </c>
+      <c r="J765" s="2">
+        <v>4.09</v>
+      </c>
+      <c r="K765" s="2">
+        <v>4.1449999999999996</v>
+      </c>
+      <c r="L765" s="9">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="M765" s="9">
+        <v>3.27</v>
+      </c>
+      <c r="N765" s="9">
+        <v>3.4350000000000001</v>
+      </c>
+      <c r="O765" s="9">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="P765" s="9">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="Q765" s="9">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="R765" s="9">
+        <v>3.5249999999999999</v>
+      </c>
+    </row>
+    <row r="766" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A766" s="4">
+        <v>46225</v>
+      </c>
+      <c r="B766" s="4">
+        <v>46225</v>
+      </c>
+      <c r="C766" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D766" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E766" s="2">
+        <v>3.4775</v>
+      </c>
+      <c r="F766" s="2">
+        <v>3.83</v>
+      </c>
+      <c r="G766" s="2">
+        <v>3.9649999999999999</v>
+      </c>
+      <c r="H766" s="2">
+        <v>4.0350000000000001</v>
+      </c>
+      <c r="I766" s="2">
+        <v>4.0824999999999996</v>
+      </c>
+      <c r="J766" s="2">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="K766" s="2">
+        <v>4.2074999999999996</v>
+      </c>
+      <c r="L766" s="9">
+        <v>3.105</v>
+      </c>
+      <c r="M766" s="9">
+        <v>3.33</v>
+      </c>
+      <c r="N766" s="9">
+        <v>3.4849999999999999</v>
+      </c>
+      <c r="O766" s="9">
+        <v>3.57</v>
+      </c>
+      <c r="P766" s="9">
+        <v>3.62</v>
+      </c>
+      <c r="Q766" s="9">
+        <v>3.66</v>
+      </c>
+      <c r="R766" s="9">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="767" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A767" s="4">
+        <v>46226</v>
+      </c>
+      <c r="B767" s="4">
+        <v>46226</v>
+      </c>
+      <c r="C767" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D767" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E767" s="2">
+        <v>3.48</v>
+      </c>
+      <c r="F767" s="2">
+        <v>3.84</v>
+      </c>
+      <c r="G767" s="2">
+        <v>3.9750000000000001</v>
+      </c>
+      <c r="H767" s="2">
+        <v>4.0425000000000004</v>
+      </c>
+      <c r="I767" s="2">
+        <v>4.0925000000000002</v>
+      </c>
+      <c r="J767" s="2">
+        <v>4.16</v>
+      </c>
+      <c r="K767" s="2">
+        <v>4.2175000000000002</v>
+      </c>
+      <c r="L767" s="9">
+        <v>3.1749999999999998</v>
+      </c>
+      <c r="M767" s="9">
+        <v>3.38</v>
+      </c>
+      <c r="N767" s="9">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="O767" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="P767" s="9">
+        <v>3.64</v>
+      </c>
+      <c r="Q767" s="9">
+        <v>3.68</v>
+      </c>
+      <c r="R767" s="9">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="768" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A768" s="4">
+        <v>46227</v>
+      </c>
+      <c r="B768" s="4">
+        <v>46227</v>
+      </c>
+      <c r="C768" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D768" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E768" s="2">
+        <v>3.5074999999999998</v>
+      </c>
+      <c r="F768" s="2">
+        <v>3.88</v>
+      </c>
+      <c r="G768" s="2">
+        <v>4.0149999999999997</v>
+      </c>
+      <c r="H768" s="2">
+        <v>4.0925000000000002</v>
+      </c>
+      <c r="I768" s="2">
+        <v>4.1425000000000001</v>
+      </c>
+      <c r="J768" s="2">
+        <v>4.2024999999999997</v>
+      </c>
+      <c r="K768" s="2">
+        <v>4.2549999999999999</v>
+      </c>
+      <c r="L768" s="9">
+        <v>3.26</v>
+      </c>
+      <c r="M768" s="9">
+        <v>3.44</v>
+      </c>
+      <c r="N768" s="9">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="O768" s="9">
+        <v>3.64</v>
+      </c>
+      <c r="P768" s="9">
+        <v>3.68</v>
+      </c>
+      <c r="Q768" s="9">
+        <v>3.72</v>
+      </c>
+      <c r="R768" s="9">
+        <v>3.625</v>
+      </c>
+    </row>
+    <row r="769" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A769" s="4">
+        <v>46230</v>
+      </c>
+      <c r="B769" s="4">
+        <v>46230</v>
+      </c>
+      <c r="C769" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D769" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E769" s="2">
+        <v>3.4624999999999999</v>
+      </c>
+      <c r="F769" s="2">
+        <v>3.8050000000000002</v>
+      </c>
+      <c r="G769" s="2">
+        <v>3.9325000000000001</v>
+      </c>
+      <c r="H769" s="2">
+        <v>4.0075000000000003</v>
+      </c>
+      <c r="I769" s="2">
+        <v>4.0575000000000001</v>
+      </c>
+      <c r="J769" s="2">
+        <v>4.1150000000000002</v>
+      </c>
+      <c r="K769" s="2">
+        <v>4.1624999999999996</v>
+      </c>
+      <c r="L769" s="9">
+        <v>3.2549999999999999</v>
+      </c>
+      <c r="M769" s="9">
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="N769" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="O769" s="9">
+        <v>3.55</v>
+      </c>
+      <c r="P769" s="9">
+        <v>3.58</v>
+      </c>
+      <c r="Q769" s="9">
+        <v>3.62</v>
+      </c>
+      <c r="R769" s="9">
+        <v>3.5249999999999999</v>
+      </c>
+    </row>
+    <row r="770" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A770" s="4">
+        <v>46231</v>
+      </c>
+      <c r="B770" s="4">
+        <v>46231</v>
+      </c>
+      <c r="C770" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D770" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E770" s="2">
+        <v>3.4474999999999998</v>
+      </c>
+      <c r="F770" s="2">
+        <v>3.77</v>
+      </c>
+      <c r="G770" s="2">
+        <v>3.89</v>
+      </c>
+      <c r="H770" s="2">
+        <v>3.9649999999999999</v>
+      </c>
+      <c r="I770" s="2">
+        <v>4.0149999999999997</v>
+      </c>
+      <c r="J770" s="2">
+        <v>4.0724999999999998</v>
+      </c>
+      <c r="K770" s="2">
+        <v>4.12</v>
+      </c>
+      <c r="L770" s="9">
+        <v>3.2749999999999999</v>
+      </c>
+      <c r="M770" s="9">
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="N770" s="9">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="O770" s="9">
+        <v>3.5449999999999999</v>
+      </c>
+      <c r="P770" s="9">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="Q770" s="9">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="R770" s="9">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="771" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A771" s="4">
+        <v>46232</v>
+      </c>
+      <c r="B771" s="4">
+        <v>46232</v>
+      </c>
+      <c r="C771" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D771" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E771" s="2">
+        <v>3.4224999999999999</v>
+      </c>
+      <c r="F771" s="2">
+        <v>3.7324999999999999</v>
+      </c>
+      <c r="G771" s="2">
+        <v>3.8525</v>
+      </c>
+      <c r="H771" s="2">
+        <v>3.92</v>
+      </c>
+      <c r="I771" s="2">
+        <v>3.9674999999999998</v>
+      </c>
+      <c r="J771" s="2">
+        <v>4.03</v>
+      </c>
+      <c r="K771" s="2">
+        <v>4.0824999999999996</v>
+      </c>
+      <c r="L771" s="9">
+        <v>3.25</v>
+      </c>
+      <c r="M771" s="9">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="N771" s="9">
+        <v>3.48</v>
+      </c>
+      <c r="O771" s="9">
+        <v>3.53</v>
+      </c>
+      <c r="P771" s="9">
+        <v>3.56</v>
+      </c>
+      <c r="Q771" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="R771" s="9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="772" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A772" s="4">
+        <v>46233</v>
+      </c>
+      <c r="B772" s="4">
+        <v>46233</v>
+      </c>
+      <c r="C772" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D772" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E772" s="2">
+        <v>3.4449999999999998</v>
+      </c>
+      <c r="F772" s="2">
+        <v>3.7625000000000002</v>
+      </c>
+      <c r="G772" s="2">
+        <v>3.89</v>
+      </c>
+      <c r="H772" s="2">
+        <v>3.96</v>
+      </c>
+      <c r="I772" s="2">
+        <v>4.01</v>
+      </c>
+      <c r="J772" s="2">
+        <v>4.0875000000000004</v>
+      </c>
+      <c r="K772" s="2">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="L772" s="9">
+        <v>3.2050000000000001</v>
+      </c>
+      <c r="M772" s="9">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="N772" s="9">
+        <v>3.49</v>
+      </c>
+      <c r="O772" s="9">
+        <v>3.55</v>
+      </c>
+      <c r="P772" s="9">
+        <v>3.5950000000000002</v>
+      </c>
+      <c r="Q772" s="9">
+        <v>3.6349999999999998</v>
+      </c>
+      <c r="R772" s="9">
+        <v>3.5350000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -43305,6 +43811,257 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B53C53-446E-4959-A400-CF5DFAD5C745}">
+  <dimension ref="B2:I10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="11">
+        <v>46223</v>
+      </c>
+      <c r="C2">
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="D2">
+        <v>3.26</v>
+      </c>
+      <c r="E2">
+        <v>3.43</v>
+      </c>
+      <c r="F2">
+        <v>3.52</v>
+      </c>
+      <c r="G2">
+        <v>3.57</v>
+      </c>
+      <c r="H2">
+        <v>3.61</v>
+      </c>
+      <c r="I2">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="11">
+        <v>46224</v>
+      </c>
+      <c r="C3">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="D3">
+        <v>3.27</v>
+      </c>
+      <c r="E3">
+        <v>3.4350000000000001</v>
+      </c>
+      <c r="F3">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="G3">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="H3">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="I3">
+        <v>3.5249999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="11">
+        <v>46225</v>
+      </c>
+      <c r="C4">
+        <v>3.105</v>
+      </c>
+      <c r="D4">
+        <v>3.33</v>
+      </c>
+      <c r="E4">
+        <v>3.4849999999999999</v>
+      </c>
+      <c r="F4">
+        <v>3.57</v>
+      </c>
+      <c r="G4">
+        <v>3.62</v>
+      </c>
+      <c r="H4">
+        <v>3.66</v>
+      </c>
+      <c r="I4">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="11">
+        <v>46226</v>
+      </c>
+      <c r="C5">
+        <v>3.1749999999999998</v>
+      </c>
+      <c r="D5">
+        <v>3.38</v>
+      </c>
+      <c r="E5">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="F5">
+        <v>3.6</v>
+      </c>
+      <c r="G5">
+        <v>3.64</v>
+      </c>
+      <c r="H5">
+        <v>3.68</v>
+      </c>
+      <c r="I5">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="11">
+        <v>46227</v>
+      </c>
+      <c r="C6">
+        <v>3.26</v>
+      </c>
+      <c r="D6">
+        <v>3.44</v>
+      </c>
+      <c r="E6">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="F6">
+        <v>3.64</v>
+      </c>
+      <c r="G6">
+        <v>3.68</v>
+      </c>
+      <c r="H6">
+        <v>3.72</v>
+      </c>
+      <c r="I6">
+        <v>3.625</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="11">
+        <v>46230</v>
+      </c>
+      <c r="C7">
+        <v>3.2549999999999999</v>
+      </c>
+      <c r="D7">
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="E7">
+        <v>3.5</v>
+      </c>
+      <c r="F7">
+        <v>3.55</v>
+      </c>
+      <c r="G7">
+        <v>3.58</v>
+      </c>
+      <c r="H7">
+        <v>3.62</v>
+      </c>
+      <c r="I7">
+        <v>3.5249999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="11">
+        <v>46231</v>
+      </c>
+      <c r="C8">
+        <v>3.2749999999999999</v>
+      </c>
+      <c r="D8">
+        <v>3.3849999999999998</v>
+      </c>
+      <c r="E8">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="F8">
+        <v>3.5449999999999999</v>
+      </c>
+      <c r="G8">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="H8">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="I8">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="11">
+        <v>46232</v>
+      </c>
+      <c r="C9">
+        <v>3.25</v>
+      </c>
+      <c r="D9">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="E9">
+        <v>3.48</v>
+      </c>
+      <c r="F9">
+        <v>3.53</v>
+      </c>
+      <c r="G9">
+        <v>3.56</v>
+      </c>
+      <c r="H9">
+        <v>3.6</v>
+      </c>
+      <c r="I9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="11">
+        <v>46233</v>
+      </c>
+      <c r="C10">
+        <v>3.2050000000000001</v>
+      </c>
+      <c r="D10">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="E10">
+        <v>3.49</v>
+      </c>
+      <c r="F10">
+        <v>3.55</v>
+      </c>
+      <c r="G10">
+        <v>3.5950000000000002</v>
+      </c>
+      <c r="H10">
+        <v>3.6349999999999998</v>
+      </c>
+      <c r="I10">
+        <v>3.5350000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:I10">
+    <sortCondition ref="B2:B10"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F7B68C-7149-4431-8318-C6CA85CD9F67}">
   <dimension ref="B2:D4"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/data_lake/fixed_income/South Korea/SwapRate.xlsx
+++ b/data_lake/fixed_income/South Korea/SwapRate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\fixed_income\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/fixed_income/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E2FC7B-DB8F-450E-9ECC-8B1985D0C686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41890353-5E01-154F-B03B-A91A977CF3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C9C890FF-C3F2-4A9F-8865-0BB25D5A743B}"/>
+    <workbookView xWindow="24640" yWindow="600" windowWidth="26560" windowHeight="24900" xr2:uid="{C9C890FF-C3F2-4A9F-8865-0BB25D5A743B}"/>
   </bookViews>
   <sheets>
     <sheet name="KR" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="27">
   <si>
     <t>https://www.kmbco.com/kor/rate/deri_rate.do#article1</t>
   </si>
@@ -148,14 +148,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,41 +214,40 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -264,9 +263,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -304,7 +303,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -410,7 +409,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -552,7 +551,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -560,19 +559,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4AAE20-6E9C-4CCD-99FF-CD3680691C67}">
-  <dimension ref="A1:R772"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R783"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" style="4" customWidth="1"/>
     <col min="5" max="11" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="11.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.77734375" style="3"/>
+    <col min="12" max="18" width="11.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18">
       <c r="A1" s="6" t="s">
         <v>7</v>
       </c>
@@ -628,7 +627,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18">
       <c r="A2" s="4">
         <v>45082</v>
       </c>
@@ -684,7 +683,7 @@
         <v>2.6349999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18">
       <c r="A3" s="4">
         <v>45084</v>
       </c>
@@ -740,7 +739,7 @@
         <v>2.6549999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18">
       <c r="A4" s="4">
         <v>45085</v>
       </c>
@@ -796,7 +795,7 @@
         <v>2.6949999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>45086</v>
       </c>
@@ -852,7 +851,7 @@
         <v>2.665</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18">
       <c r="A6" s="4">
         <v>45089</v>
       </c>
@@ -908,7 +907,7 @@
         <v>2.625</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18">
       <c r="A7" s="4">
         <v>45090</v>
       </c>
@@ -964,7 +963,7 @@
         <v>2.6850000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18">
       <c r="A8" s="4">
         <v>45091</v>
       </c>
@@ -1020,7 +1019,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18">
       <c r="A9" s="4">
         <v>45092</v>
       </c>
@@ -1076,7 +1075,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18">
       <c r="A10" s="4">
         <v>45093</v>
       </c>
@@ -1132,7 +1131,7 @@
         <v>2.8149999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18">
       <c r="A11" s="4">
         <v>45096</v>
       </c>
@@ -1188,7 +1187,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18">
       <c r="A12" s="4">
         <v>45097</v>
       </c>
@@ -1244,7 +1243,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18">
       <c r="A13" s="4">
         <v>45098</v>
       </c>
@@ -1300,7 +1299,7 @@
         <v>2.835</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18">
       <c r="A14" s="4">
         <v>45099</v>
       </c>
@@ -1356,7 +1355,7 @@
         <v>2.8450000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18">
       <c r="A15" s="4">
         <v>45100</v>
       </c>
@@ -1412,7 +1411,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18">
       <c r="A16" s="4">
         <v>45103</v>
       </c>
@@ -1468,7 +1467,7 @@
         <v>2.7850000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18">
       <c r="A17" s="4">
         <v>45104</v>
       </c>
@@ -1524,7 +1523,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18">
       <c r="A18" s="4">
         <v>45105</v>
       </c>
@@ -1580,7 +1579,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18">
       <c r="A19" s="4">
         <v>45106</v>
       </c>
@@ -1636,7 +1635,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18">
       <c r="A20" s="4">
         <v>45107</v>
       </c>
@@ -1692,7 +1691,7 @@
         <v>2.875</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18">
       <c r="A21" s="4">
         <v>45110</v>
       </c>
@@ -1748,7 +1747,7 @@
         <v>2.8650000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18">
       <c r="A22" s="4">
         <v>45111</v>
       </c>
@@ -1804,7 +1803,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18">
       <c r="A23" s="4">
         <v>45112</v>
       </c>
@@ -1860,7 +1859,7 @@
         <v>2.8849999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18">
       <c r="A24" s="4">
         <v>45113</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18">
       <c r="A25" s="4">
         <v>45114</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>2.9649999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18">
       <c r="A26" s="4">
         <v>45117</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>3.0649999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18">
       <c r="A27" s="4">
         <v>45118</v>
       </c>
@@ -2084,7 +2083,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18">
       <c r="A28" s="4">
         <v>45119</v>
       </c>
@@ -2140,7 +2139,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18">
       <c r="A29" s="4">
         <v>45120</v>
       </c>
@@ -2196,7 +2195,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18">
       <c r="A30" s="4">
         <v>45121</v>
       </c>
@@ -2252,7 +2251,7 @@
         <v>2.9449999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18">
       <c r="A31" s="4">
         <v>45124</v>
       </c>
@@ -2308,7 +2307,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18">
       <c r="A32" s="4">
         <v>45125</v>
       </c>
@@ -2364,7 +2363,7 @@
         <v>2.9350000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18">
       <c r="A33" s="4">
         <v>45126</v>
       </c>
@@ -2420,7 +2419,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18">
       <c r="A34" s="4">
         <v>45127</v>
       </c>
@@ -2476,7 +2475,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18">
       <c r="A35" s="4">
         <v>45128</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>2.9750000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18">
       <c r="A36" s="4">
         <v>45131</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>2.9550000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18">
       <c r="A37" s="4">
         <v>45132</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18">
       <c r="A38" s="4">
         <v>45133</v>
       </c>
@@ -2700,7 +2699,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18">
       <c r="A39" s="4">
         <v>45134</v>
       </c>
@@ -2756,7 +2755,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18">
       <c r="A40" s="4">
         <v>45135</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>2.8849999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18">
       <c r="A41" s="4">
         <v>45138</v>
       </c>
@@ -2868,7 +2867,7 @@
         <v>2.9649999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18">
       <c r="A42" s="4">
         <v>45139</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>2.9950000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18">
       <c r="A43" s="4">
         <v>45140</v>
       </c>
@@ -2980,7 +2979,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18">
       <c r="A44" s="4">
         <v>45141</v>
       </c>
@@ -3036,7 +3035,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18">
       <c r="A45" s="4">
         <v>45142</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18">
       <c r="A46" s="4">
         <v>45145</v>
       </c>
@@ -3148,7 +3147,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18">
       <c r="A47" s="4">
         <v>45146</v>
       </c>
@@ -3204,7 +3203,7 @@
         <v>2.9750000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18">
       <c r="A48" s="4">
         <v>45147</v>
       </c>
@@ -3260,7 +3259,7 @@
         <v>2.9649999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18">
       <c r="A49" s="4">
         <v>45148</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>2.9550000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18">
       <c r="A50" s="4">
         <v>45149</v>
       </c>
@@ -3372,7 +3371,7 @@
         <v>2.9350000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18">
       <c r="A51" s="4">
         <v>45152</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>2.9550000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18">
       <c r="A52" s="4">
         <v>45154</v>
       </c>
@@ -3484,7 +3483,7 @@
         <v>2.9249999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18">
       <c r="A53" s="4">
         <v>45155</v>
       </c>
@@ -3540,7 +3539,7 @@
         <v>3.0350000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18">
       <c r="A54" s="4">
         <v>45156</v>
       </c>
@@ -3596,7 +3595,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18">
       <c r="A55" s="4">
         <v>45159</v>
       </c>
@@ -3652,7 +3651,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18">
       <c r="A56" s="4">
         <v>45160</v>
       </c>
@@ -3708,7 +3707,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18">
       <c r="A57" s="4">
         <v>45161</v>
       </c>
@@ -3764,7 +3763,7 @@
         <v>3.0550000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18">
       <c r="A58" s="4">
         <v>45162</v>
       </c>
@@ -3820,7 +3819,7 @@
         <v>3.0150000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18">
       <c r="A59" s="4">
         <v>45163</v>
       </c>
@@ -3876,7 +3875,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18">
       <c r="A60" s="4">
         <v>45166</v>
       </c>
@@ -3932,7 +3931,7 @@
         <v>3.0950000000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18">
       <c r="A61" s="4">
         <v>45167</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>3.0950000000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18">
       <c r="A62" s="4">
         <v>45168</v>
       </c>
@@ -4044,7 +4043,7 @@
         <v>3.0950000000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18">
       <c r="A63" s="4">
         <v>45169</v>
       </c>
@@ -4100,7 +4099,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18">
       <c r="A64" s="4">
         <v>45170</v>
       </c>
@@ -4156,7 +4155,7 @@
         <v>3.0449999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18">
       <c r="A65" s="4">
         <v>45173</v>
       </c>
@@ -4212,7 +4211,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18">
       <c r="A66" s="4">
         <v>45174</v>
       </c>
@@ -4268,7 +4267,7 @@
         <v>3.0449999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18">
       <c r="A67" s="4">
         <v>45175</v>
       </c>
@@ -4324,7 +4323,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18">
       <c r="A68" s="4">
         <v>45176</v>
       </c>
@@ -4380,7 +4379,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18">
       <c r="A69" s="4">
         <v>45177</v>
       </c>
@@ -4436,7 +4435,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18">
       <c r="A70" s="4">
         <v>45180</v>
       </c>
@@ -4492,7 +4491,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18">
       <c r="A71" s="4">
         <v>45181</v>
       </c>
@@ -4548,7 +4547,7 @@
         <v>3.2050000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18">
       <c r="A72" s="4">
         <v>45182</v>
       </c>
@@ -4604,7 +4603,7 @@
         <v>3.2250000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18">
       <c r="A73" s="4">
         <v>45183</v>
       </c>
@@ -4660,7 +4659,7 @@
         <v>3.2349999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18">
       <c r="A74" s="4">
         <v>45184</v>
       </c>
@@ -4716,7 +4715,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18">
       <c r="A75" s="4">
         <v>45187</v>
       </c>
@@ -4772,7 +4771,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18">
       <c r="A76" s="4">
         <v>45188</v>
       </c>
@@ -4828,7 +4827,7 @@
         <v>3.2450000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18">
       <c r="A77" s="4">
         <v>45189</v>
       </c>
@@ -4884,7 +4883,7 @@
         <v>3.2349999999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18">
       <c r="A78" s="4">
         <v>45190</v>
       </c>
@@ -4940,7 +4939,7 @@
         <v>3.2450000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18">
       <c r="A79" s="4">
         <v>45191</v>
       </c>
@@ -4996,7 +4995,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18">
       <c r="A80" s="4">
         <v>45194</v>
       </c>
@@ -5052,7 +5051,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18">
       <c r="A81" s="4">
         <v>45195</v>
       </c>
@@ -5108,7 +5107,7 @@
         <v>3.1850000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18">
       <c r="A82" s="4">
         <v>45196</v>
       </c>
@@ -5164,7 +5163,7 @@
         <v>3.125</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18">
       <c r="A83" s="4">
         <v>45203</v>
       </c>
@@ -5220,7 +5219,7 @@
         <v>3.3450000000000002</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18">
       <c r="A84" s="4">
         <v>45204</v>
       </c>
@@ -5276,7 +5275,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18">
       <c r="A85" s="4">
         <v>45205</v>
       </c>
@@ -5332,7 +5331,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18">
       <c r="A86" s="4">
         <v>45209</v>
       </c>
@@ -5388,7 +5387,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18">
       <c r="A87" s="4">
         <v>45210</v>
       </c>
@@ -5444,7 +5443,7 @@
         <v>3.145</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18">
       <c r="A88" s="4">
         <v>45211</v>
       </c>
@@ -5500,7 +5499,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18">
       <c r="A89" s="4">
         <v>45212</v>
       </c>
@@ -5556,7 +5555,7 @@
         <v>3.1749999999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18">
       <c r="A90" s="4">
         <v>45215</v>
       </c>
@@ -5612,7 +5611,7 @@
         <v>3.1850000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18">
       <c r="A91" s="4">
         <v>45216</v>
       </c>
@@ -5668,7 +5667,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18">
       <c r="A92" s="4">
         <v>45217</v>
       </c>
@@ -5724,7 +5723,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18">
       <c r="A93" s="4">
         <v>45218</v>
       </c>
@@ -5780,7 +5779,7 @@
         <v>3.3149999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18">
       <c r="A94" s="4">
         <v>45219</v>
       </c>
@@ -5836,7 +5835,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18">
       <c r="A95" s="4">
         <v>45222</v>
       </c>
@@ -5892,7 +5891,7 @@
         <v>3.4049999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18">
       <c r="A96" s="4">
         <v>45223</v>
       </c>
@@ -5948,7 +5947,7 @@
         <v>3.355</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18">
       <c r="A97" s="4">
         <v>45224</v>
       </c>
@@ -6004,7 +6003,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18">
       <c r="A98" s="4">
         <v>45225</v>
       </c>
@@ -6060,7 +6059,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18">
       <c r="A99" s="4">
         <v>45226</v>
       </c>
@@ -6116,7 +6115,7 @@
         <v>3.355</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18">
       <c r="A100" s="4">
         <v>45229</v>
       </c>
@@ -6172,7 +6171,7 @@
         <v>3.3450000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18">
       <c r="A101" s="4">
         <v>45230</v>
       </c>
@@ -6228,7 +6227,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18">
       <c r="A102" s="4">
         <v>45231</v>
       </c>
@@ -6284,7 +6283,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18">
       <c r="A103" s="4">
         <v>45232</v>
       </c>
@@ -6340,7 +6339,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18">
       <c r="A104" s="4">
         <v>45233</v>
       </c>
@@ -6396,7 +6395,7 @@
         <v>3.2949999999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18">
       <c r="A105" s="4">
         <v>45236</v>
       </c>
@@ -6452,7 +6451,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18">
       <c r="A106" s="4">
         <v>45237</v>
       </c>
@@ -6508,7 +6507,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18">
       <c r="A107" s="4">
         <v>45238</v>
       </c>
@@ -6564,7 +6563,7 @@
         <v>3.2549999999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18">
       <c r="A108" s="4">
         <v>45239</v>
       </c>
@@ -6620,7 +6619,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18">
       <c r="A109" s="4">
         <v>45240</v>
       </c>
@@ -6676,7 +6675,7 @@
         <v>3.2450000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18">
       <c r="A110" s="4">
         <v>45243</v>
       </c>
@@ -6732,7 +6731,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18">
       <c r="A111" s="4">
         <v>45244</v>
       </c>
@@ -6788,7 +6787,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18">
       <c r="A112" s="4">
         <v>45245</v>
       </c>
@@ -6844,7 +6843,7 @@
         <v>3.0150000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18">
       <c r="A113" s="4">
         <v>45246</v>
       </c>
@@ -6900,7 +6899,7 @@
         <v>2.9550000000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18">
       <c r="A114" s="4">
         <v>45247</v>
       </c>
@@ -6956,7 +6955,7 @@
         <v>2.9350000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18">
       <c r="A115" s="4">
         <v>45250</v>
       </c>
@@ -7012,7 +7011,7 @@
         <v>2.8849999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18">
       <c r="A116" s="4">
         <v>45251</v>
       </c>
@@ -7068,7 +7067,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18">
       <c r="A117" s="4">
         <v>45252</v>
       </c>
@@ -7124,7 +7123,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18">
       <c r="A118" s="4">
         <v>45253</v>
       </c>
@@ -7180,7 +7179,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18">
       <c r="A119" s="4">
         <v>45254</v>
       </c>
@@ -7236,7 +7235,7 @@
         <v>2.855</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18">
       <c r="A120" s="4">
         <v>45257</v>
       </c>
@@ -7292,7 +7291,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18">
       <c r="A121" s="4">
         <v>45258</v>
       </c>
@@ -7348,7 +7347,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18">
       <c r="A122" s="4">
         <v>45259</v>
       </c>
@@ -7404,7 +7403,7 @@
         <v>2.645</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18">
       <c r="A123" s="4">
         <v>45260</v>
       </c>
@@ -7460,7 +7459,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18">
       <c r="A124" s="4">
         <v>45261</v>
       </c>
@@ -7516,7 +7515,7 @@
         <v>2.7349999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18">
       <c r="A125" s="4">
         <v>45264</v>
       </c>
@@ -7572,7 +7571,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18">
       <c r="A126" s="4">
         <v>45265</v>
       </c>
@@ -7628,7 +7627,7 @@
         <v>2.5750000000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18">
       <c r="A127" s="4">
         <v>45266</v>
       </c>
@@ -7684,7 +7683,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18">
       <c r="A128" s="4">
         <v>45267</v>
       </c>
@@ -7740,7 +7739,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18">
       <c r="A129" s="4">
         <v>45268</v>
       </c>
@@ -7796,7 +7795,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18">
       <c r="A130" s="4">
         <v>45271</v>
       </c>
@@ -7852,7 +7851,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18">
       <c r="A131" s="4">
         <v>45272</v>
       </c>
@@ -7908,7 +7907,7 @@
         <v>2.5649999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18">
       <c r="A132" s="4">
         <v>45273</v>
       </c>
@@ -7964,7 +7963,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18">
       <c r="A133" s="4">
         <v>45274</v>
       </c>
@@ -8020,7 +8019,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18">
       <c r="A134" s="4">
         <v>45275</v>
       </c>
@@ -8076,7 +8075,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18">
       <c r="A135" s="4">
         <v>45278</v>
       </c>
@@ -8132,7 +8131,7 @@
         <v>2.4449999999999998</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18">
       <c r="A136" s="4">
         <v>45279</v>
       </c>
@@ -8188,7 +8187,7 @@
         <v>2.4649999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18">
       <c r="A137" s="4">
         <v>45280</v>
       </c>
@@ -8244,7 +8243,7 @@
         <v>2.4249999999999998</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18">
       <c r="A138" s="4">
         <v>45281</v>
       </c>
@@ -8300,7 +8299,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18">
       <c r="A139" s="4">
         <v>45282</v>
       </c>
@@ -8356,7 +8355,7 @@
         <v>2.3450000000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18">
       <c r="A140" s="4">
         <v>45286</v>
       </c>
@@ -8412,7 +8411,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18">
       <c r="A141" s="4">
         <v>45287</v>
       </c>
@@ -8468,7 +8467,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18">
       <c r="A142" s="4">
         <v>45288</v>
       </c>
@@ -8524,7 +8523,7 @@
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18">
       <c r="A143" s="4">
         <v>45289</v>
       </c>
@@ -8580,7 +8579,7 @@
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18">
       <c r="A144" s="4">
         <v>45293</v>
       </c>
@@ -8636,7 +8635,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18">
       <c r="A145" s="4">
         <v>45294</v>
       </c>
@@ -8692,7 +8691,7 @@
         <v>2.415</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18">
       <c r="A146" s="4">
         <v>45295</v>
       </c>
@@ -8748,7 +8747,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18">
       <c r="A147" s="4">
         <v>45296</v>
       </c>
@@ -8804,7 +8803,7 @@
         <v>2.5750000000000002</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18">
       <c r="A148" s="4">
         <v>45299</v>
       </c>
@@ -8860,7 +8859,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18">
       <c r="A149" s="4">
         <v>45300</v>
       </c>
@@ -8916,7 +8915,7 @@
         <v>2.5750000000000002</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18">
       <c r="A150" s="4">
         <v>45301</v>
       </c>
@@ -8972,7 +8971,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18">
       <c r="A151" s="4">
         <v>45302</v>
       </c>
@@ -9028,7 +9027,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18">
       <c r="A152" s="4">
         <v>45303</v>
       </c>
@@ -9084,7 +9083,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18">
       <c r="A153" s="4">
         <v>45306</v>
       </c>
@@ -9140,7 +9139,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18">
       <c r="A154" s="4">
         <v>45307</v>
       </c>
@@ -9196,7 +9195,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18">
       <c r="A155" s="4">
         <v>45308</v>
       </c>
@@ -9252,7 +9251,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18">
       <c r="A156" s="4">
         <v>45309</v>
       </c>
@@ -9308,7 +9307,7 @@
         <v>2.585</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18">
       <c r="A157" s="4">
         <v>45310</v>
       </c>
@@ -9364,7 +9363,7 @@
         <v>2.625</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18">
       <c r="A158" s="4">
         <v>45313</v>
       </c>
@@ -9420,7 +9419,7 @@
         <v>2.5950000000000002</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18">
       <c r="A159" s="4">
         <v>45314</v>
       </c>
@@ -9476,7 +9475,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18">
       <c r="A160" s="4">
         <v>45315</v>
       </c>
@@ -9532,7 +9531,7 @@
         <v>2.625</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18">
       <c r="A161" s="4">
         <v>45316</v>
       </c>
@@ -9588,7 +9587,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18">
       <c r="A162" s="4">
         <v>45317</v>
       </c>
@@ -9644,7 +9643,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18">
       <c r="A163" s="4">
         <v>45320</v>
       </c>
@@ -9700,7 +9699,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18">
       <c r="A164" s="4">
         <v>45321</v>
       </c>
@@ -9756,7 +9755,7 @@
         <v>2.5449999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18">
       <c r="A165" s="4">
         <v>45322</v>
       </c>
@@ -9812,7 +9811,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18">
       <c r="A166" s="4">
         <v>45323</v>
       </c>
@@ -9868,7 +9867,7 @@
         <v>2.4550000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18">
       <c r="A167" s="4">
         <v>45324</v>
       </c>
@@ -9924,7 +9923,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18">
       <c r="A168" s="4">
         <v>45327</v>
       </c>
@@ -9980,7 +9979,7 @@
         <v>2.4849999999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18">
       <c r="A169" s="4">
         <v>45328</v>
       </c>
@@ -10036,7 +10035,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18">
       <c r="A170" s="4">
         <v>45329</v>
       </c>
@@ -10092,7 +10091,7 @@
         <v>2.5150000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18">
       <c r="A171" s="4">
         <v>45330</v>
       </c>
@@ -10148,7 +10147,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18">
       <c r="A172" s="4">
         <v>45335</v>
       </c>
@@ -10204,7 +10203,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18">
       <c r="A173" s="4">
         <v>45336</v>
       </c>
@@ -10260,7 +10259,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18">
       <c r="A174" s="4">
         <v>45337</v>
       </c>
@@ -10316,7 +10315,7 @@
         <v>2.7149999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18">
       <c r="A175" s="4">
         <v>45338</v>
       </c>
@@ -10372,7 +10371,7 @@
         <v>2.7450000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18">
       <c r="A176" s="4">
         <v>45341</v>
       </c>
@@ -10428,7 +10427,7 @@
         <v>2.7250000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18">
       <c r="A177" s="4">
         <v>45342</v>
       </c>
@@ -10484,7 +10483,7 @@
         <v>2.7349999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18">
       <c r="A178" s="4">
         <v>45343</v>
       </c>
@@ -10540,7 +10539,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18">
       <c r="A179" s="4">
         <v>45344</v>
       </c>
@@ -10596,7 +10595,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18">
       <c r="A180" s="4">
         <v>45345</v>
       </c>
@@ -10652,7 +10651,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18">
       <c r="A181" s="4">
         <v>45348</v>
       </c>
@@ -10708,7 +10707,7 @@
         <v>2.665</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18">
       <c r="A182" s="4">
         <v>45349</v>
       </c>
@@ -10764,7 +10763,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18">
       <c r="A183" s="4">
         <v>45350</v>
       </c>
@@ -10820,7 +10819,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18">
       <c r="A184" s="4">
         <v>45351</v>
       </c>
@@ -10876,7 +10875,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18">
       <c r="A185" s="4">
         <v>45355</v>
       </c>
@@ -10932,7 +10931,7 @@
         <v>2.645</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18">
       <c r="A186" s="4">
         <v>45356</v>
       </c>
@@ -10988,7 +10987,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18">
       <c r="A187" s="4">
         <v>45357</v>
       </c>
@@ -11044,7 +11043,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18">
       <c r="A188" s="4">
         <v>45358</v>
       </c>
@@ -11100,7 +11099,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18">
       <c r="A189" s="4">
         <v>45359</v>
       </c>
@@ -11156,7 +11155,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18">
       <c r="A190" s="4">
         <v>45362</v>
       </c>
@@ -11212,7 +11211,7 @@
         <v>2.6349999999999998</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18">
       <c r="A191" s="4">
         <v>45363</v>
       </c>
@@ -11268,7 +11267,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18">
       <c r="A192" s="4">
         <v>45364</v>
       </c>
@@ -11324,7 +11323,7 @@
         <v>2.625</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18">
       <c r="A193" s="4">
         <v>45365</v>
       </c>
@@ -11380,7 +11379,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18">
       <c r="A194" s="4">
         <v>45366</v>
       </c>
@@ -11436,7 +11435,7 @@
         <v>2.645</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18">
       <c r="A195" s="4">
         <v>45369</v>
       </c>
@@ -11492,7 +11491,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18">
       <c r="A196" s="4">
         <v>45370</v>
       </c>
@@ -11548,7 +11547,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18">
       <c r="A197" s="4">
         <v>45371</v>
       </c>
@@ -11604,7 +11603,7 @@
         <v>2.7050000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18">
       <c r="A198" s="4">
         <v>45372</v>
       </c>
@@ -11660,7 +11659,7 @@
         <v>2.645</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18">
       <c r="A199" s="4">
         <v>45373</v>
       </c>
@@ -11716,7 +11715,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18">
       <c r="A200" s="4">
         <v>45376</v>
       </c>
@@ -11772,7 +11771,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18">
       <c r="A201" s="4">
         <v>45377</v>
       </c>
@@ -11828,7 +11827,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18">
       <c r="A202" s="4">
         <v>45378</v>
       </c>
@@ -11884,7 +11883,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18">
       <c r="A203" s="4">
         <v>45379</v>
       </c>
@@ -11940,7 +11939,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18">
       <c r="A204" s="4">
         <v>45380</v>
       </c>
@@ -11996,7 +11995,7 @@
         <v>2.6549999999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18">
       <c r="A205" s="4">
         <v>45383</v>
       </c>
@@ -12052,7 +12051,7 @@
         <v>2.625</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18">
       <c r="A206" s="4">
         <v>45384</v>
       </c>
@@ -12108,7 +12107,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18">
       <c r="A207" s="4">
         <v>45385</v>
       </c>
@@ -12164,7 +12163,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18">
       <c r="A208" s="4">
         <v>45386</v>
       </c>
@@ -12220,7 +12219,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18">
       <c r="A209" s="4">
         <v>45387</v>
       </c>
@@ -12276,7 +12275,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18">
       <c r="A210" s="4">
         <v>45390</v>
       </c>
@@ -12332,7 +12331,7 @@
         <v>2.665</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18">
       <c r="A211" s="4">
         <v>45391</v>
       </c>
@@ -12388,7 +12387,7 @@
         <v>2.7250000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18">
       <c r="A212" s="4">
         <v>45393</v>
       </c>
@@ -12444,7 +12443,7 @@
         <v>2.7949999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18">
       <c r="A213" s="4">
         <v>45394</v>
       </c>
@@ -12500,7 +12499,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18">
       <c r="A214" s="4">
         <v>45397</v>
       </c>
@@ -12556,7 +12555,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18">
       <c r="A215" s="4">
         <v>45398</v>
       </c>
@@ -12612,7 +12611,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18">
       <c r="A216" s="4">
         <v>45399</v>
       </c>
@@ -12668,7 +12667,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18">
       <c r="A217" s="4">
         <v>45400</v>
       </c>
@@ -12724,7 +12723,7 @@
         <v>2.8250000000000002</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18">
       <c r="A218" s="4">
         <v>45401</v>
       </c>
@@ -12780,7 +12779,7 @@
         <v>2.7949999999999999</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18">
       <c r="A219" s="4">
         <v>45404</v>
       </c>
@@ -12836,7 +12835,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18">
       <c r="A220" s="4">
         <v>45405</v>
       </c>
@@ -12892,7 +12891,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18">
       <c r="A221" s="4">
         <v>45406</v>
       </c>
@@ -12948,7 +12947,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18">
       <c r="A222" s="4">
         <v>45407</v>
       </c>
@@ -13004,7 +13003,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18">
       <c r="A223" s="4">
         <v>45408</v>
       </c>
@@ -13060,7 +13059,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18">
       <c r="A224" s="4">
         <v>45411</v>
       </c>
@@ -13116,7 +13115,7 @@
         <v>2.875</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18">
       <c r="A225" s="4">
         <v>45412</v>
       </c>
@@ -13172,7 +13171,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18">
       <c r="A226" s="4">
         <v>45414</v>
       </c>
@@ -13228,7 +13227,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:18">
       <c r="A227" s="4">
         <v>45415</v>
       </c>
@@ -13284,7 +13283,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18">
       <c r="A228" s="4">
         <v>45419</v>
       </c>
@@ -13340,7 +13339,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18">
       <c r="A229" s="4">
         <v>45420</v>
       </c>
@@ -13396,7 +13395,7 @@
         <v>2.7650000000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18">
       <c r="A230" s="4">
         <v>45421</v>
       </c>
@@ -13452,7 +13451,7 @@
         <v>2.7749999999999999</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18">
       <c r="A231" s="4">
         <v>45422</v>
       </c>
@@ -13508,7 +13507,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18">
       <c r="A232" s="4">
         <v>45425</v>
       </c>
@@ -13564,7 +13563,7 @@
         <v>2.7549999999999999</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18">
       <c r="A233" s="4">
         <v>45426</v>
       </c>
@@ -13620,7 +13619,7 @@
         <v>2.7549999999999999</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18">
       <c r="A234" s="4">
         <v>45428</v>
       </c>
@@ -13676,7 +13675,7 @@
         <v>2.6749999999999998</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18">
       <c r="A235" s="4">
         <v>45429</v>
       </c>
@@ -13732,7 +13731,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18">
       <c r="A236" s="4">
         <v>45432</v>
       </c>
@@ -13788,7 +13787,7 @@
         <v>2.665</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18">
       <c r="A237" s="4">
         <v>45433</v>
       </c>
@@ -13844,7 +13843,7 @@
         <v>2.6549999999999998</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18">
       <c r="A238" s="4">
         <v>45434</v>
       </c>
@@ -13900,7 +13899,7 @@
         <v>2.645</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18">
       <c r="A239" s="4">
         <v>45435</v>
       </c>
@@ -13956,7 +13955,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18">
       <c r="A240" s="4">
         <v>45436</v>
       </c>
@@ -14012,7 +14011,7 @@
         <v>2.665</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18">
       <c r="A241" s="4">
         <v>45439</v>
       </c>
@@ -14068,7 +14067,7 @@
         <v>2.665</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18">
       <c r="A242" s="4">
         <v>45440</v>
       </c>
@@ -14124,7 +14123,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18">
       <c r="A243" s="4">
         <v>45441</v>
       </c>
@@ -14180,7 +14179,7 @@
         <v>2.6949999999999998</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18">
       <c r="A244" s="4">
         <v>45442</v>
       </c>
@@ -14236,7 +14235,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18">
       <c r="A245" s="4">
         <v>45443</v>
       </c>
@@ -14292,7 +14291,7 @@
         <v>2.7450000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18">
       <c r="A246" s="4">
         <v>45446</v>
       </c>
@@ -14348,7 +14347,7 @@
         <v>2.7050000000000001</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18">
       <c r="A247" s="4">
         <v>45447</v>
       </c>
@@ -14404,7 +14403,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18">
       <c r="A248" s="4">
         <v>45448</v>
       </c>
@@ -14460,7 +14459,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18">
       <c r="A249" s="4">
         <v>45450</v>
       </c>
@@ -14516,7 +14515,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18">
       <c r="A250" s="4">
         <v>45453</v>
       </c>
@@ -14572,7 +14571,7 @@
         <v>2.6150000000000002</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18">
       <c r="A251" s="4">
         <v>45454</v>
       </c>
@@ -14628,7 +14627,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18">
       <c r="A252" s="4">
         <v>45455</v>
       </c>
@@ -14684,7 +14683,7 @@
         <v>2.585</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18">
       <c r="A253" s="4">
         <v>45456</v>
       </c>
@@ -14740,7 +14739,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18">
       <c r="A254" s="4">
         <v>45457</v>
       </c>
@@ -14796,7 +14795,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:18">
       <c r="A255" s="4">
         <v>45460</v>
       </c>
@@ -14852,7 +14851,7 @@
         <v>2.4649999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18">
       <c r="A256" s="4">
         <v>45461</v>
       </c>
@@ -14908,7 +14907,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18">
       <c r="A257" s="4">
         <v>45462</v>
       </c>
@@ -14964,7 +14963,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:18">
       <c r="A258" s="4">
         <v>45463</v>
       </c>
@@ -15020,7 +15019,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:18">
       <c r="A259" s="4">
         <v>45464</v>
       </c>
@@ -15076,7 +15075,7 @@
         <v>2.5649999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18">
       <c r="A260" s="4">
         <v>45467</v>
       </c>
@@ -15132,7 +15131,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18">
       <c r="A261" s="4">
         <v>45468</v>
       </c>
@@ -15188,7 +15187,7 @@
         <v>2.5449999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:18">
       <c r="A262" s="4">
         <v>45469</v>
       </c>
@@ -15244,7 +15243,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:18">
       <c r="A263" s="4">
         <v>45470</v>
       </c>
@@ -15300,7 +15299,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:18">
       <c r="A264" s="4">
         <v>45471</v>
       </c>
@@ -15356,7 +15355,7 @@
         <v>2.5150000000000001</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:18">
       <c r="A265" s="4">
         <v>45474</v>
       </c>
@@ -15412,7 +15411,7 @@
         <v>2.5350000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:18">
       <c r="A266" s="4">
         <v>45475</v>
       </c>
@@ -15468,7 +15467,7 @@
         <v>2.4750000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18">
       <c r="A267" s="4">
         <v>45476</v>
       </c>
@@ -15524,7 +15523,7 @@
         <v>2.4449999999999998</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18">
       <c r="A268" s="4">
         <v>45477</v>
       </c>
@@ -15580,7 +15579,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18">
       <c r="A269" s="4">
         <v>45478</v>
       </c>
@@ -15636,7 +15635,7 @@
         <v>2.4049999999999998</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18">
       <c r="A270" s="4">
         <v>45481</v>
       </c>
@@ -15692,7 +15691,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18">
       <c r="A271" s="4">
         <v>45482</v>
       </c>
@@ -15748,7 +15747,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18">
       <c r="A272" s="4">
         <v>45483</v>
       </c>
@@ -15804,7 +15803,7 @@
         <v>2.395</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:18">
       <c r="A273" s="4">
         <v>45484</v>
       </c>
@@ -15860,7 +15859,7 @@
         <v>2.4449999999999998</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:18">
       <c r="A274" s="4">
         <v>45485</v>
       </c>
@@ -15916,7 +15915,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:18">
       <c r="A275" s="4">
         <v>45488</v>
       </c>
@@ -15972,7 +15971,7 @@
         <v>2.395</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:18">
       <c r="A276" s="4">
         <v>45489</v>
       </c>
@@ -16028,7 +16027,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:18">
       <c r="A277" s="4">
         <v>45490</v>
       </c>
@@ -16084,7 +16083,7 @@
         <v>2.355</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:18">
       <c r="A278" s="4">
         <v>45491</v>
       </c>
@@ -16140,7 +16139,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:18">
       <c r="A279" s="4">
         <v>45492</v>
       </c>
@@ -16196,7 +16195,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:18">
       <c r="A280" s="4">
         <v>45495</v>
       </c>
@@ -16252,7 +16251,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:18">
       <c r="A281" s="4">
         <v>45496</v>
       </c>
@@ -16308,7 +16307,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:18">
       <c r="A282" s="4">
         <v>45497</v>
       </c>
@@ -16364,7 +16363,7 @@
         <v>2.335</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:18">
       <c r="A283" s="4">
         <v>45498</v>
       </c>
@@ -16420,7 +16419,7 @@
         <v>2.3050000000000002</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:18">
       <c r="A284" s="4">
         <v>45499</v>
       </c>
@@ -16476,7 +16475,7 @@
         <v>2.3149999999999999</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:18">
       <c r="A285" s="4">
         <v>45502</v>
       </c>
@@ -16532,7 +16531,7 @@
         <v>2.2850000000000001</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:18">
       <c r="A286" s="4">
         <v>45503</v>
       </c>
@@ -16588,7 +16587,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:18">
       <c r="A287" s="4">
         <v>45504</v>
       </c>
@@ -16644,7 +16643,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:18">
       <c r="A288" s="4">
         <v>45505</v>
       </c>
@@ -16700,7 +16699,7 @@
         <v>2.2450000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:18">
       <c r="A289" s="4">
         <v>45506</v>
       </c>
@@ -16756,7 +16755,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:18">
       <c r="A290" s="4">
         <v>45509</v>
       </c>
@@ -16812,7 +16811,7 @@
         <v>2.0150000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:18">
       <c r="A291" s="4">
         <v>45510</v>
       </c>
@@ -16868,7 +16867,7 @@
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:18">
       <c r="A292" s="4">
         <v>45511</v>
       </c>
@@ -16924,7 +16923,7 @@
         <v>2.1349999999999998</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:18">
       <c r="A293" s="4">
         <v>45512</v>
       </c>
@@ -16980,7 +16979,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:18">
       <c r="A294" s="4">
         <v>45513</v>
       </c>
@@ -17036,7 +17035,7 @@
         <v>2.165</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:18">
       <c r="A295" s="4">
         <v>45516</v>
       </c>
@@ -17092,7 +17091,7 @@
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:18">
       <c r="A296" s="4">
         <v>45517</v>
       </c>
@@ -17148,7 +17147,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:18">
       <c r="A297" s="4">
         <v>45518</v>
       </c>
@@ -17204,7 +17203,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:18">
       <c r="A298" s="4">
         <v>45520</v>
       </c>
@@ -17260,7 +17259,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:18">
       <c r="A299" s="4">
         <v>45523</v>
       </c>
@@ -17316,7 +17315,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:18">
       <c r="A300" s="4">
         <v>45524</v>
       </c>
@@ -17372,7 +17371,7 @@
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:18">
       <c r="A301" s="4">
         <v>45525</v>
       </c>
@@ -17428,7 +17427,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:18">
       <c r="A302" s="4">
         <v>45526</v>
       </c>
@@ -17484,7 +17483,7 @@
         <v>2.1949999999999998</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:18">
       <c r="A303" s="4">
         <v>45527</v>
       </c>
@@ -17540,7 +17539,7 @@
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:18">
       <c r="A304" s="4">
         <v>45530</v>
       </c>
@@ -17596,7 +17595,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:18">
       <c r="A305" s="4">
         <v>45531</v>
       </c>
@@ -17652,7 +17651,7 @@
         <v>2.2149999999999999</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:18">
       <c r="A306" s="4">
         <v>45532</v>
       </c>
@@ -17708,7 +17707,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:18">
       <c r="A307" s="4">
         <v>45533</v>
       </c>
@@ -17764,7 +17763,7 @@
         <v>2.2349999999999999</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:18">
       <c r="A308" s="4">
         <v>45534</v>
       </c>
@@ -17820,7 +17819,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:18">
       <c r="A309" s="4">
         <v>45537</v>
       </c>
@@ -17876,7 +17875,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:18">
       <c r="A310" s="4">
         <v>45538</v>
       </c>
@@ -17932,7 +17931,7 @@
         <v>2.2850000000000001</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:18">
       <c r="A311" s="4">
         <v>45539</v>
       </c>
@@ -17988,7 +17987,7 @@
         <v>2.2450000000000001</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:18">
       <c r="A312" s="4">
         <v>45540</v>
       </c>
@@ -18044,7 +18043,7 @@
         <v>2.1949999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:18">
       <c r="A313" s="4">
         <v>45541</v>
       </c>
@@ -18100,7 +18099,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:18">
       <c r="A314" s="4">
         <v>45544</v>
       </c>
@@ -18156,7 +18155,7 @@
         <v>2.1949999999999998</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:18">
       <c r="A315" s="4">
         <v>45545</v>
       </c>
@@ -18212,7 +18211,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:18">
       <c r="A316" s="4">
         <v>45546</v>
       </c>
@@ -18268,7 +18267,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:18">
       <c r="A317" s="4">
         <v>45547</v>
       </c>
@@ -18324,7 +18323,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:18">
       <c r="A318" s="4">
         <v>45548</v>
       </c>
@@ -18380,7 +18379,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:18">
       <c r="A319" s="4">
         <v>45554</v>
       </c>
@@ -18436,7 +18435,7 @@
         <v>2.145</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:18">
       <c r="A320" s="4">
         <v>45555</v>
       </c>
@@ -18492,7 +18491,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:18">
       <c r="A321" s="4">
         <v>45558</v>
       </c>
@@ -18548,7 +18547,7 @@
         <v>2.2149999999999999</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:18">
       <c r="A322" s="4">
         <v>45559</v>
       </c>
@@ -18604,7 +18603,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:18">
       <c r="A323" s="4">
         <v>45560</v>
       </c>
@@ -18660,7 +18659,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:18">
       <c r="A324" s="4">
         <v>45561</v>
       </c>
@@ -18716,7 +18715,7 @@
         <v>2.2250000000000001</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:18">
       <c r="A325" s="4">
         <v>45562</v>
       </c>
@@ -18772,7 +18771,7 @@
         <v>2.2349999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:18">
       <c r="A326" s="4">
         <v>45565</v>
       </c>
@@ -18828,7 +18827,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:18">
       <c r="A327" s="4">
         <v>45567</v>
       </c>
@@ -18884,7 +18883,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:18">
       <c r="A328" s="4">
         <v>45569</v>
       </c>
@@ -18940,7 +18939,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:18">
       <c r="A329" s="4">
         <v>45572</v>
       </c>
@@ -18996,7 +18995,7 @@
         <v>2.395</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:18">
       <c r="A330" s="4">
         <v>45573</v>
       </c>
@@ -19052,7 +19051,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:18">
       <c r="A331" s="4">
         <v>45575</v>
       </c>
@@ -19108,7 +19107,7 @@
         <v>2.4049999999999998</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:18">
       <c r="A332" s="4">
         <v>45576</v>
       </c>
@@ -19164,7 +19163,7 @@
         <v>2.395</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:18">
       <c r="A333" s="4">
         <v>45579</v>
       </c>
@@ -19220,7 +19219,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:18">
       <c r="A334" s="4">
         <v>45580</v>
       </c>
@@ -19276,7 +19275,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:18">
       <c r="A335" s="4">
         <v>45581</v>
       </c>
@@ -19332,7 +19331,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:18">
       <c r="A336" s="4">
         <v>45582</v>
       </c>
@@ -19388,7 +19387,7 @@
         <v>2.2850000000000001</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:18">
       <c r="A337" s="4">
         <v>45583</v>
       </c>
@@ -19444,7 +19443,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:18">
       <c r="A338" s="4">
         <v>45586</v>
       </c>
@@ -19500,7 +19499,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:18">
       <c r="A339" s="4">
         <v>45587</v>
       </c>
@@ -19556,7 +19555,7 @@
         <v>2.3650000000000002</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:18">
       <c r="A340" s="4">
         <v>45588</v>
       </c>
@@ -19612,7 +19611,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:18">
       <c r="A341" s="4">
         <v>45589</v>
       </c>
@@ -19668,7 +19667,7 @@
         <v>2.2850000000000001</v>
       </c>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:18">
       <c r="A342" s="4">
         <v>45590</v>
       </c>
@@ -19724,7 +19723,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:18">
       <c r="A343" s="4">
         <v>45593</v>
       </c>
@@ -19780,7 +19779,7 @@
         <v>2.335</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:18">
       <c r="A344" s="4">
         <v>45594</v>
       </c>
@@ -19836,7 +19835,7 @@
         <v>2.335</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:18">
       <c r="A345" s="4">
         <v>45595</v>
       </c>
@@ -19892,7 +19891,7 @@
         <v>2.355</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:18">
       <c r="A346" s="4">
         <v>45596</v>
       </c>
@@ -19948,7 +19947,7 @@
         <v>2.335</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:18">
       <c r="A347" s="4">
         <v>45597</v>
       </c>
@@ -20004,7 +20003,7 @@
         <v>2.335</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:18">
       <c r="A348" s="4">
         <v>45600</v>
       </c>
@@ -20060,7 +20059,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:18">
       <c r="A349" s="4">
         <v>45601</v>
       </c>
@@ -20116,7 +20115,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:18">
       <c r="A350" s="4">
         <v>45602</v>
       </c>
@@ -20172,7 +20171,7 @@
         <v>2.3149999999999999</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:18">
       <c r="A351" s="4">
         <v>45603</v>
       </c>
@@ -20228,7 +20227,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:18">
       <c r="A352" s="4">
         <v>45604</v>
       </c>
@@ -20284,7 +20283,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:18">
       <c r="A353" s="4">
         <v>45607</v>
       </c>
@@ -20340,7 +20339,7 @@
         <v>2.3050000000000002</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:18">
       <c r="A354" s="4">
         <v>45608</v>
       </c>
@@ -20396,7 +20395,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:18">
       <c r="A355" s="4">
         <v>45609</v>
       </c>
@@ -20452,7 +20451,7 @@
         <v>2.335</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:18">
       <c r="A356" s="4">
         <v>45610</v>
       </c>
@@ -20508,7 +20507,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:18">
       <c r="A357" s="4">
         <v>45611</v>
       </c>
@@ -20564,7 +20563,7 @@
         <v>2.335</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:18">
       <c r="A358" s="4">
         <v>45614</v>
       </c>
@@ -20620,7 +20619,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:18">
       <c r="A359" s="4">
         <v>45615</v>
       </c>
@@ -20676,7 +20675,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:18">
       <c r="A360" s="4">
         <v>45616</v>
       </c>
@@ -20732,7 +20731,7 @@
         <v>2.2749999999999999</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:18">
       <c r="A361" s="4">
         <v>45617</v>
       </c>
@@ -20788,7 +20787,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:18">
       <c r="A362" s="4">
         <v>45618</v>
       </c>
@@ -20844,7 +20843,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:18">
       <c r="A363" s="4">
         <v>45621</v>
       </c>
@@ -20900,7 +20899,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:18">
       <c r="A364" s="4">
         <v>45622</v>
       </c>
@@ -20956,7 +20955,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:18">
       <c r="A365" s="4">
         <v>45623</v>
       </c>
@@ -21012,7 +21011,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="366" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:18">
       <c r="A366" s="4">
         <v>45624</v>
       </c>
@@ -21068,7 +21067,7 @@
         <v>2.105</v>
       </c>
     </row>
-    <row r="367" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:18">
       <c r="A367" s="4">
         <v>45625</v>
       </c>
@@ -21124,7 +21123,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="368" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:18">
       <c r="A368" s="4">
         <v>45628</v>
       </c>
@@ -21180,7 +21179,7 @@
         <v>2.0049999999999999</v>
       </c>
     </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:18">
       <c r="A369" s="4">
         <v>45629</v>
       </c>
@@ -21236,7 +21235,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:18">
       <c r="A370" s="4">
         <v>45630</v>
       </c>
@@ -21292,7 +21291,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:18">
       <c r="A371" s="4">
         <v>45631</v>
       </c>
@@ -21348,7 +21347,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:18">
       <c r="A372" s="4">
         <v>45632</v>
       </c>
@@ -21404,7 +21403,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:18">
       <c r="A373" s="4">
         <v>45635</v>
       </c>
@@ -21460,7 +21459,7 @@
         <v>1.875</v>
       </c>
     </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:18">
       <c r="A374" s="4">
         <v>45636</v>
       </c>
@@ -21516,7 +21515,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:18">
       <c r="A375" s="4">
         <v>45637</v>
       </c>
@@ -21572,7 +21571,7 @@
         <v>1.9450000000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:18">
       <c r="A376" s="4">
         <v>45638</v>
       </c>
@@ -21628,7 +21627,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:18">
       <c r="A377" s="4">
         <v>45639</v>
       </c>
@@ -21684,7 +21683,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:18">
       <c r="A378" s="4">
         <v>45642</v>
       </c>
@@ -21740,7 +21739,7 @@
         <v>2.0150000000000001</v>
       </c>
     </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:18">
       <c r="A379" s="4">
         <v>45643</v>
       </c>
@@ -21796,7 +21795,7 @@
         <v>2.085</v>
       </c>
     </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:18">
       <c r="A380" s="4">
         <v>45644</v>
       </c>
@@ -21852,7 +21851,7 @@
         <v>2.0550000000000002</v>
       </c>
     </row>
-    <row r="381" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:18">
       <c r="A381" s="4">
         <v>45645</v>
       </c>
@@ -21908,7 +21907,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="382" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:18">
       <c r="A382" s="4">
         <v>45646</v>
       </c>
@@ -21964,7 +21963,7 @@
         <v>2.1349999999999998</v>
       </c>
     </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:18">
       <c r="A383" s="4">
         <v>45649</v>
       </c>
@@ -22020,7 +22019,7 @@
         <v>2.1349999999999998</v>
       </c>
     </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:18">
       <c r="A384" s="4">
         <v>45650</v>
       </c>
@@ -22076,7 +22075,7 @@
         <v>2.1749999999999998</v>
       </c>
     </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:18">
       <c r="A385" s="4">
         <v>45652</v>
       </c>
@@ -22132,7 +22131,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:18">
       <c r="A386" s="4">
         <v>45653</v>
       </c>
@@ -22188,7 +22187,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:18">
       <c r="A387" s="4">
         <v>45656</v>
       </c>
@@ -22244,7 +22243,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:18">
       <c r="A388" s="4">
         <v>45657</v>
       </c>
@@ -22300,7 +22299,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="389" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:18">
       <c r="A389" s="4">
         <v>45659</v>
       </c>
@@ -22356,7 +22355,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="390" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:18">
       <c r="A390" s="4">
         <v>45660</v>
       </c>
@@ -22412,7 +22411,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="391" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:18">
       <c r="A391" s="4">
         <v>45663</v>
       </c>
@@ -22468,7 +22467,7 @@
         <v>2.1850000000000001</v>
       </c>
     </row>
-    <row r="392" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:18">
       <c r="A392" s="4">
         <v>45664</v>
       </c>
@@ -22524,7 +22523,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="393" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:18">
       <c r="A393" s="4">
         <v>45665</v>
       </c>
@@ -22580,7 +22579,7 @@
         <v>2.1749999999999998</v>
       </c>
     </row>
-    <row r="394" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:18">
       <c r="A394" s="4">
         <v>45666</v>
       </c>
@@ -22636,7 +22635,7 @@
         <v>2.165</v>
       </c>
     </row>
-    <row r="395" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:18">
       <c r="A395" s="4">
         <v>45667</v>
       </c>
@@ -22692,7 +22691,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="396" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:18">
       <c r="A396" s="4">
         <v>45670</v>
       </c>
@@ -22748,7 +22747,7 @@
         <v>2.3250000000000002</v>
       </c>
     </row>
-    <row r="397" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:18">
       <c r="A397" s="4">
         <v>45671</v>
       </c>
@@ -22804,7 +22803,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="398" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:18">
       <c r="A398" s="4">
         <v>45672</v>
       </c>
@@ -22860,7 +22859,7 @@
         <v>2.2749999999999999</v>
       </c>
     </row>
-    <row r="399" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:18">
       <c r="A399" s="4">
         <v>45673</v>
       </c>
@@ -22916,7 +22915,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="400" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:18">
       <c r="A400" s="4">
         <v>45674</v>
       </c>
@@ -22972,7 +22971,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="401" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:18">
       <c r="A401" s="4">
         <v>45677</v>
       </c>
@@ -23028,7 +23027,7 @@
         <v>2.145</v>
       </c>
     </row>
-    <row r="402" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:18">
       <c r="A402" s="4">
         <v>45678</v>
       </c>
@@ -23084,7 +23083,7 @@
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="403" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:18">
       <c r="A403" s="4">
         <v>45679</v>
       </c>
@@ -23140,7 +23139,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="404" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:18">
       <c r="A404" s="4">
         <v>45680</v>
       </c>
@@ -23196,7 +23195,7 @@
         <v>2.145</v>
       </c>
     </row>
-    <row r="405" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:18">
       <c r="A405" s="4">
         <v>45681</v>
       </c>
@@ -23252,7 +23251,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="406" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:18">
       <c r="A406" s="4">
         <v>45688</v>
       </c>
@@ -23308,7 +23307,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="407" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:18">
       <c r="A407" s="4">
         <v>45691</v>
       </c>
@@ -23364,7 +23363,7 @@
         <v>2.145</v>
       </c>
     </row>
-    <row r="408" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:18">
       <c r="A408" s="4">
         <v>45692</v>
       </c>
@@ -23420,7 +23419,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="409" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:18">
       <c r="A409" s="4">
         <v>45693</v>
       </c>
@@ -23476,7 +23475,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="410" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:18">
       <c r="A410" s="4">
         <v>45694</v>
       </c>
@@ -23532,7 +23531,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="411" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:18">
       <c r="A411" s="4">
         <v>45695</v>
       </c>
@@ -23588,7 +23587,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="412" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:18">
       <c r="A412" s="4">
         <v>45698</v>
       </c>
@@ -23644,7 +23643,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="413" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:18">
       <c r="A413" s="4">
         <v>45699</v>
       </c>
@@ -23700,7 +23699,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="414" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:18">
       <c r="A414" s="4">
         <v>45700</v>
       </c>
@@ -23756,7 +23755,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="415" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:18">
       <c r="A415" s="4">
         <v>45701</v>
       </c>
@@ -23812,7 +23811,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="416" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:18">
       <c r="A416" s="4">
         <v>45702</v>
       </c>
@@ -23868,7 +23867,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="417" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:18">
       <c r="A417" s="4">
         <v>45705</v>
       </c>
@@ -23924,7 +23923,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="418" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:18">
       <c r="A418" s="4">
         <v>45706</v>
       </c>
@@ -23980,7 +23979,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="419" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:18">
       <c r="A419" s="4">
         <v>45707</v>
       </c>
@@ -24036,7 +24035,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="420" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:18">
       <c r="A420" s="4">
         <v>45708</v>
       </c>
@@ -24092,7 +24091,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="421" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:18">
       <c r="A421" s="4">
         <v>45709</v>
       </c>
@@ -24148,7 +24147,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="422" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:18">
       <c r="A422" s="4">
         <v>45712</v>
       </c>
@@ -24204,7 +24203,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="423" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:18">
       <c r="A423" s="4">
         <v>45713</v>
       </c>
@@ -24260,7 +24259,7 @@
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="424" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:18">
       <c r="A424" s="4">
         <v>45714</v>
       </c>
@@ -24316,7 +24315,7 @@
         <v>2.0750000000000002</v>
       </c>
     </row>
-    <row r="425" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:18">
       <c r="A425" s="4">
         <v>45715</v>
       </c>
@@ -24372,7 +24371,7 @@
         <v>2.0550000000000002</v>
       </c>
     </row>
-    <row r="426" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:18">
       <c r="A426" s="4">
         <v>45716</v>
       </c>
@@ -24428,7 +24427,7 @@
         <v>2.0150000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:18">
       <c r="A427" s="4">
         <v>45720</v>
       </c>
@@ -24484,7 +24483,7 @@
         <v>1.9950000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:18">
       <c r="A428" s="4">
         <v>45721</v>
       </c>
@@ -24540,7 +24539,7 @@
         <v>2.0049999999999999</v>
       </c>
     </row>
-    <row r="429" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:18">
       <c r="A429" s="4">
         <v>45722</v>
       </c>
@@ -24596,7 +24595,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="430" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:18">
       <c r="A430" s="4">
         <v>45723</v>
       </c>
@@ -24652,7 +24651,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="431" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:18">
       <c r="A431" s="4">
         <v>45726</v>
       </c>
@@ -24708,7 +24707,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="432" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:18">
       <c r="A432" s="4">
         <v>45727</v>
       </c>
@@ -24764,7 +24763,7 @@
         <v>1.9450000000000001</v>
       </c>
     </row>
-    <row r="433" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:18">
       <c r="A433" s="4">
         <v>45728</v>
       </c>
@@ -24820,7 +24819,7 @@
         <v>1.9650000000000001</v>
       </c>
     </row>
-    <row r="434" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:18">
       <c r="A434" s="4">
         <v>45729</v>
       </c>
@@ -24876,7 +24875,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="435" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:18">
       <c r="A435" s="4">
         <v>45730</v>
       </c>
@@ -24932,7 +24931,7 @@
         <v>2.0750000000000002</v>
       </c>
     </row>
-    <row r="436" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:18">
       <c r="A436" s="4">
         <v>45733</v>
       </c>
@@ -24988,7 +24987,7 @@
         <v>2.0750000000000002</v>
       </c>
     </row>
-    <row r="437" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:18">
       <c r="A437" s="4">
         <v>45734</v>
       </c>
@@ -25044,7 +25043,7 @@
         <v>2.085</v>
       </c>
     </row>
-    <row r="438" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:18">
       <c r="A438" s="4">
         <v>45735</v>
       </c>
@@ -25100,7 +25099,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="439" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:18">
       <c r="A439" s="4">
         <v>45736</v>
       </c>
@@ -25156,7 +25155,7 @@
         <v>2.165</v>
       </c>
     </row>
-    <row r="440" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:18">
       <c r="A440" s="4">
         <v>45737</v>
       </c>
@@ -25212,7 +25211,7 @@
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="441" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:18">
       <c r="A441" s="4">
         <v>45740</v>
       </c>
@@ -25268,7 +25267,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="442" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:18">
       <c r="A442" s="4">
         <v>45741</v>
       </c>
@@ -25324,7 +25323,7 @@
         <v>2.3250000000000002</v>
       </c>
     </row>
-    <row r="443" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:18">
       <c r="A443" s="4">
         <v>45742</v>
       </c>
@@ -25380,7 +25379,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="444" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:18">
       <c r="A444" s="4">
         <v>45743</v>
       </c>
@@ -25436,7 +25435,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="445" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:18">
       <c r="A445" s="4">
         <v>45744</v>
       </c>
@@ -25492,7 +25491,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="446" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:18">
       <c r="A446" s="4">
         <v>45747</v>
       </c>
@@ -25548,7 +25547,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="447" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:18">
       <c r="A447" s="4">
         <v>45748</v>
       </c>
@@ -25604,7 +25603,7 @@
         <v>2.2749999999999999</v>
       </c>
     </row>
-    <row r="448" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:18">
       <c r="A448" s="4">
         <v>45749</v>
       </c>
@@ -25660,7 +25659,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="449" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:18">
       <c r="A449" s="4">
         <v>45750</v>
       </c>
@@ -25716,7 +25715,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="450" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:18">
       <c r="A450" s="4">
         <v>45751</v>
       </c>
@@ -25772,7 +25771,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="451" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:18">
       <c r="A451" s="4">
         <v>45754</v>
       </c>
@@ -25828,7 +25827,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="452" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:18">
       <c r="A452" s="4">
         <v>45755</v>
       </c>
@@ -25884,7 +25883,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="453" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:18">
       <c r="A453" s="4">
         <v>45756</v>
       </c>
@@ -25940,7 +25939,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="454" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:18">
       <c r="A454" s="4">
         <v>45757</v>
       </c>
@@ -25996,7 +25995,7 @@
         <v>1.9950000000000001</v>
       </c>
     </row>
-    <row r="455" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:18">
       <c r="A455" s="4">
         <v>45758</v>
       </c>
@@ -26052,7 +26051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="456" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:18">
       <c r="A456" s="4">
         <v>45761</v>
       </c>
@@ -26108,7 +26107,7 @@
         <v>2.0049999999999999</v>
       </c>
     </row>
-    <row r="457" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:18">
       <c r="A457" s="4">
         <v>45762</v>
       </c>
@@ -26164,7 +26163,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="458" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:18">
       <c r="A458" s="4">
         <v>45763</v>
       </c>
@@ -26220,7 +26219,7 @@
         <v>1.9550000000000001</v>
       </c>
     </row>
-    <row r="459" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:18">
       <c r="A459" s="4">
         <v>45764</v>
       </c>
@@ -26276,7 +26275,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="460" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:18">
       <c r="A460" s="4">
         <v>45765</v>
       </c>
@@ -26332,7 +26331,7 @@
         <v>1.9550000000000001</v>
       </c>
     </row>
-    <row r="461" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:18">
       <c r="A461" s="4">
         <v>45768</v>
       </c>
@@ -26388,7 +26387,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="462" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:18">
       <c r="A462" s="4">
         <v>45769</v>
       </c>
@@ -26444,7 +26443,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="463" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:18">
       <c r="A463" s="4">
         <v>45770</v>
       </c>
@@ -26500,7 +26499,7 @@
         <v>1.905</v>
       </c>
     </row>
-    <row r="464" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:18">
       <c r="A464" s="4">
         <v>45771</v>
       </c>
@@ -26556,7 +26555,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="465" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:18">
       <c r="A465" s="4">
         <v>45772</v>
       </c>
@@ -26612,7 +26611,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="466" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:18">
       <c r="A466" s="4">
         <v>45775</v>
       </c>
@@ -26668,7 +26667,7 @@
         <v>1.9450000000000001</v>
       </c>
     </row>
-    <row r="467" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:18">
       <c r="A467" s="4">
         <v>45776</v>
       </c>
@@ -26724,7 +26723,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="468" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:18">
       <c r="A468" s="4">
         <v>45777</v>
       </c>
@@ -26780,7 +26779,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="469" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:18">
       <c r="A469" s="4">
         <v>45779</v>
       </c>
@@ -26836,7 +26835,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="470" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:18">
       <c r="A470" s="4">
         <v>45784</v>
       </c>
@@ -26892,7 +26891,7 @@
         <v>1.9650000000000001</v>
       </c>
     </row>
-    <row r="471" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:18">
       <c r="A471" s="4">
         <v>45785</v>
       </c>
@@ -26948,7 +26947,7 @@
         <v>1.9850000000000001</v>
       </c>
     </row>
-    <row r="472" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:18">
       <c r="A472" s="4">
         <v>45786</v>
       </c>
@@ -27004,7 +27003,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="473" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:18">
       <c r="A473" s="4">
         <v>45789</v>
       </c>
@@ -27060,7 +27059,7 @@
         <v>1.9950000000000001</v>
       </c>
     </row>
-    <row r="474" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:18">
       <c r="A474" s="4">
         <v>45790</v>
       </c>
@@ -27116,7 +27115,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="475" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:18">
       <c r="A475" s="4">
         <v>45791</v>
       </c>
@@ -27172,7 +27171,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="476" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:18">
       <c r="A476" s="4">
         <v>45792</v>
       </c>
@@ -27228,7 +27227,7 @@
         <v>2.0049999999999999</v>
       </c>
     </row>
-    <row r="477" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:18">
       <c r="A477" s="4">
         <v>45793</v>
       </c>
@@ -27284,7 +27283,7 @@
         <v>1.9550000000000001</v>
       </c>
     </row>
-    <row r="478" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:18">
       <c r="A478" s="4">
         <v>45796</v>
       </c>
@@ -27340,7 +27339,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="479" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:18">
       <c r="A479" s="4">
         <v>45797</v>
       </c>
@@ -27396,7 +27395,7 @@
         <v>1.9650000000000001</v>
       </c>
     </row>
-    <row r="480" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:18">
       <c r="A480" s="4">
         <v>45798</v>
       </c>
@@ -27452,7 +27451,7 @@
         <v>1.9550000000000001</v>
       </c>
     </row>
-    <row r="481" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:18">
       <c r="A481" s="4">
         <v>45799</v>
       </c>
@@ -27508,7 +27507,7 @@
         <v>1.9650000000000001</v>
       </c>
     </row>
-    <row r="482" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:18">
       <c r="A482" s="4">
         <v>45800</v>
       </c>
@@ -27564,7 +27563,7 @@
         <v>1.9750000000000001</v>
       </c>
     </row>
-    <row r="483" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:18">
       <c r="A483" s="4">
         <v>45803</v>
       </c>
@@ -27620,7 +27619,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="484" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:18">
       <c r="A484" s="4">
         <v>45804</v>
       </c>
@@ -27676,7 +27675,7 @@
         <v>1.9650000000000001</v>
       </c>
     </row>
-    <row r="485" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:18">
       <c r="A485" s="4">
         <v>45805</v>
       </c>
@@ -27732,7 +27731,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="486" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:18">
       <c r="A486" s="4">
         <v>45806</v>
       </c>
@@ -27788,7 +27787,7 @@
         <v>1.9450000000000001</v>
       </c>
     </row>
-    <row r="487" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:18">
       <c r="A487" s="4">
         <v>45807</v>
       </c>
@@ -27844,7 +27843,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="488" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:18">
       <c r="A488" s="4">
         <v>45810</v>
       </c>
@@ -27900,7 +27899,7 @@
         <v>1.925</v>
       </c>
     </row>
-    <row r="489" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:18">
       <c r="A489" s="4">
         <v>45812</v>
       </c>
@@ -27956,7 +27955,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="490" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:18">
       <c r="A490" s="4">
         <v>45813</v>
       </c>
@@ -28012,7 +28011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:18">
       <c r="A491" s="4">
         <v>45817</v>
       </c>
@@ -28068,7 +28067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:18">
       <c r="A492" s="4">
         <v>45818</v>
       </c>
@@ -28124,7 +28123,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="493" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:18">
       <c r="A493" s="4">
         <v>45819</v>
       </c>
@@ -28180,7 +28179,7 @@
         <v>2.0449999999999999</v>
       </c>
     </row>
-    <row r="494" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:18">
       <c r="A494" s="4">
         <v>45820</v>
       </c>
@@ -28236,7 +28235,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="495" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:18">
       <c r="A495" s="4">
         <v>45821</v>
       </c>
@@ -28292,7 +28291,7 @@
         <v>2.0049999999999999</v>
       </c>
     </row>
-    <row r="496" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:18">
       <c r="A496" s="4">
         <v>45824</v>
       </c>
@@ -28348,7 +28347,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="497" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:18">
       <c r="A497" s="4">
         <v>45825</v>
       </c>
@@ -28404,7 +28403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:18">
       <c r="A498" s="4">
         <v>45826</v>
       </c>
@@ -28460,7 +28459,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="499" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:18">
       <c r="A499" s="4">
         <v>45827</v>
       </c>
@@ -28516,7 +28515,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="500" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:18">
       <c r="A500" s="4">
         <v>45828</v>
       </c>
@@ -28572,7 +28571,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="501" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:18">
       <c r="A501" s="4">
         <v>45831</v>
       </c>
@@ -28628,7 +28627,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="502" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:18">
       <c r="A502" s="4">
         <v>45832</v>
       </c>
@@ -28684,7 +28683,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="503" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:18">
       <c r="A503" s="4">
         <v>45833</v>
       </c>
@@ -28740,7 +28739,7 @@
         <v>2.0550000000000002</v>
       </c>
     </row>
-    <row r="504" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:18">
       <c r="A504" s="4">
         <v>45834</v>
       </c>
@@ -28796,7 +28795,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="505" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:18">
       <c r="A505" s="4">
         <v>45835</v>
       </c>
@@ -28852,7 +28851,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="506" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:18">
       <c r="A506" s="4">
         <v>45838</v>
       </c>
@@ -28908,7 +28907,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="507" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:18">
       <c r="A507" s="4">
         <v>45839</v>
       </c>
@@ -28964,7 +28963,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="508" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:18">
       <c r="A508" s="4">
         <v>45840</v>
       </c>
@@ -29020,7 +29019,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="509" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:18">
       <c r="A509" s="4">
         <v>45841</v>
       </c>
@@ -29076,7 +29075,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="510" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:18">
       <c r="A510" s="4">
         <v>45842</v>
       </c>
@@ -29132,7 +29131,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="511" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:18">
       <c r="A511" s="4">
         <v>45845</v>
       </c>
@@ -29188,7 +29187,7 @@
         <v>2.0750000000000002</v>
       </c>
     </row>
-    <row r="512" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:18">
       <c r="A512" s="4">
         <v>45846</v>
       </c>
@@ -29244,7 +29243,7 @@
         <v>2.0550000000000002</v>
       </c>
     </row>
-    <row r="513" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:18">
       <c r="A513" s="4">
         <v>45847</v>
       </c>
@@ -29300,7 +29299,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="514" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:18">
       <c r="A514" s="4">
         <v>45848</v>
       </c>
@@ -29356,7 +29355,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="515" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:18">
       <c r="A515" s="4">
         <v>45849</v>
       </c>
@@ -29412,7 +29411,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="516" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:18">
       <c r="A516" s="4">
         <v>45852</v>
       </c>
@@ -29468,7 +29467,7 @@
         <v>2.0550000000000002</v>
       </c>
     </row>
-    <row r="517" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:18">
       <c r="A517" s="4">
         <v>45853</v>
       </c>
@@ -29524,7 +29523,7 @@
         <v>2.0449999999999999</v>
       </c>
     </row>
-    <row r="518" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:18">
       <c r="A518" s="4">
         <v>45854</v>
       </c>
@@ -29580,7 +29579,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="519" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:18">
       <c r="A519" s="4">
         <v>45855</v>
       </c>
@@ -29636,7 +29635,7 @@
         <v>2.0950000000000002</v>
       </c>
     </row>
-    <row r="520" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:18">
       <c r="A520" s="4">
         <v>45856</v>
       </c>
@@ -29692,7 +29691,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="521" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:18">
       <c r="A521" s="4">
         <v>45859</v>
       </c>
@@ -29748,7 +29747,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="522" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:18">
       <c r="A522" s="4">
         <v>45860</v>
       </c>
@@ -29804,7 +29803,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="523" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:18">
       <c r="A523" s="4">
         <v>45861</v>
       </c>
@@ -29860,7 +29859,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="524" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:18">
       <c r="A524" s="4">
         <v>45862</v>
       </c>
@@ -29916,7 +29915,7 @@
         <v>2.0750000000000002</v>
       </c>
     </row>
-    <row r="525" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:18">
       <c r="A525" s="4">
         <v>45863</v>
       </c>
@@ -29972,7 +29971,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="526" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:18">
       <c r="A526" s="4">
         <v>45866</v>
       </c>
@@ -30028,7 +30027,7 @@
         <v>2.0649999999999999</v>
       </c>
     </row>
-    <row r="527" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:18">
       <c r="A527" s="4">
         <v>45867</v>
       </c>
@@ -30084,7 +30083,7 @@
         <v>2.0649999999999999</v>
       </c>
     </row>
-    <row r="528" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:18">
       <c r="A528" s="4">
         <v>45868</v>
       </c>
@@ -30140,7 +30139,7 @@
         <v>2.085</v>
       </c>
     </row>
-    <row r="529" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:18">
       <c r="A529" s="4">
         <v>45869</v>
       </c>
@@ -30196,7 +30195,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="530" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:18">
       <c r="A530" s="4">
         <v>45870</v>
       </c>
@@ -30252,7 +30251,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="531" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:18">
       <c r="A531" s="4">
         <v>45873</v>
       </c>
@@ -30308,7 +30307,7 @@
         <v>2.1349999999999998</v>
       </c>
     </row>
-    <row r="532" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:18">
       <c r="A532" s="4">
         <v>45874</v>
       </c>
@@ -30364,7 +30363,7 @@
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="533" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:18">
       <c r="A533" s="4">
         <v>45875</v>
       </c>
@@ -30420,7 +30419,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="534" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:18">
       <c r="A534" s="4">
         <v>45876</v>
       </c>
@@ -30476,7 +30475,7 @@
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="535" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:18">
       <c r="A535" s="4">
         <v>45877</v>
       </c>
@@ -30532,7 +30531,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="536" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:18">
       <c r="A536" s="4">
         <v>45880</v>
       </c>
@@ -30588,7 +30587,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="537" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:18">
       <c r="A537" s="4">
         <v>45881</v>
       </c>
@@ -30644,7 +30643,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="538" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:18">
       <c r="A538" s="4">
         <v>45882</v>
       </c>
@@ -30700,7 +30699,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="539" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:18">
       <c r="A539" s="4">
         <v>45883</v>
       </c>
@@ -30756,7 +30755,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="540" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:18">
       <c r="A540" s="4">
         <v>45887</v>
       </c>
@@ -30812,7 +30811,7 @@
         <v>2.0750000000000002</v>
       </c>
     </row>
-    <row r="541" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:18">
       <c r="A541" s="4">
         <v>45888</v>
       </c>
@@ -30868,7 +30867,7 @@
         <v>2.0950000000000002</v>
       </c>
     </row>
-    <row r="542" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:18">
       <c r="A542" s="4">
         <v>45889</v>
       </c>
@@ -30924,7 +30923,7 @@
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="543" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:18">
       <c r="A543" s="4">
         <v>45890</v>
       </c>
@@ -30980,7 +30979,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="544" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:18">
       <c r="A544" s="4">
         <v>45891</v>
       </c>
@@ -31036,7 +31035,7 @@
         <v>2.1549999999999998</v>
       </c>
     </row>
-    <row r="545" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:18">
       <c r="A545" s="4">
         <v>45894</v>
       </c>
@@ -31092,7 +31091,7 @@
         <v>2.145</v>
       </c>
     </row>
-    <row r="546" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:18">
       <c r="A546" s="4">
         <v>45895</v>
       </c>
@@ -31148,7 +31147,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="547" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:18">
       <c r="A547" s="4">
         <v>45896</v>
       </c>
@@ -31204,7 +31203,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="548" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:18">
       <c r="A548" s="4">
         <v>45897</v>
       </c>
@@ -31260,7 +31259,7 @@
         <v>2.105</v>
       </c>
     </row>
-    <row r="549" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:18">
       <c r="A549" s="4">
         <v>45898</v>
       </c>
@@ -31316,7 +31315,7 @@
         <v>2.125</v>
       </c>
     </row>
-    <row r="550" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:18">
       <c r="A550" s="4">
         <v>45901</v>
       </c>
@@ -31372,7 +31371,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="551" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:18">
       <c r="A551" s="4">
         <v>45902</v>
       </c>
@@ -31428,7 +31427,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="552" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:18">
       <c r="A552" s="4">
         <v>45903</v>
       </c>
@@ -31484,7 +31483,7 @@
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="553" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:18">
       <c r="A553" s="4">
         <v>45904</v>
       </c>
@@ -31540,7 +31539,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="554" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:18">
       <c r="A554" s="4">
         <v>45905</v>
       </c>
@@ -31596,7 +31595,7 @@
         <v>2.165</v>
       </c>
     </row>
-    <row r="555" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:18">
       <c r="A555" s="4">
         <v>45908</v>
       </c>
@@ -31652,7 +31651,7 @@
         <v>2.145</v>
       </c>
     </row>
-    <row r="556" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:18">
       <c r="A556" s="4">
         <v>45909</v>
       </c>
@@ -31708,7 +31707,7 @@
         <v>2.105</v>
       </c>
     </row>
-    <row r="557" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:18">
       <c r="A557" s="4">
         <v>45910</v>
       </c>
@@ -31764,7 +31763,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="558" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:18">
       <c r="A558" s="4">
         <v>45911</v>
       </c>
@@ -31820,7 +31819,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="559" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:18">
       <c r="A559" s="4">
         <v>45912</v>
       </c>
@@ -31876,7 +31875,7 @@
         <v>2.0649999999999999</v>
       </c>
     </row>
-    <row r="560" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:18">
       <c r="A560" s="4">
         <v>45915</v>
       </c>
@@ -31932,7 +31931,7 @@
         <v>2.0649999999999999</v>
       </c>
     </row>
-    <row r="561" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:18">
       <c r="A561" s="4">
         <v>45916</v>
       </c>
@@ -31988,7 +31987,7 @@
         <v>2.0350000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:18">
       <c r="A562" s="4">
         <v>45917</v>
       </c>
@@ -32044,7 +32043,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="563" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:18">
       <c r="A563" s="4">
         <v>45918</v>
       </c>
@@ -32100,7 +32099,7 @@
         <v>1.9850000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:18">
       <c r="A564" s="4">
         <v>45919</v>
       </c>
@@ -32156,7 +32155,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="565" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:18">
       <c r="A565" s="4">
         <v>45922</v>
       </c>
@@ -32212,7 +32211,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="566" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:18">
       <c r="A566" s="4">
         <v>45923</v>
       </c>
@@ -32268,7 +32267,7 @@
         <v>2.0249999999999999</v>
       </c>
     </row>
-    <row r="567" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:18">
       <c r="A567" s="4">
         <v>45924</v>
       </c>
@@ -32324,7 +32323,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="568" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:18">
       <c r="A568" s="4">
         <v>45925</v>
       </c>
@@ -32380,7 +32379,7 @@
         <v>2.1349999999999998</v>
       </c>
     </row>
-    <row r="569" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:18">
       <c r="A569" s="4">
         <v>45926</v>
       </c>
@@ -32436,7 +32435,7 @@
         <v>2.1150000000000002</v>
       </c>
     </row>
-    <row r="570" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:18">
       <c r="A570" s="4">
         <v>45929</v>
       </c>
@@ -32492,7 +32491,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="571" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:18">
       <c r="A571" s="4">
         <v>45930</v>
       </c>
@@ -32548,7 +32547,7 @@
         <v>2.0950000000000002</v>
       </c>
     </row>
-    <row r="572" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:18">
       <c r="A572" s="4">
         <v>45931</v>
       </c>
@@ -32604,7 +32603,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="573" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:18">
       <c r="A573" s="4">
         <v>45932</v>
       </c>
@@ -32660,7 +32659,7 @@
         <v>2.105</v>
       </c>
     </row>
-    <row r="574" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:18">
       <c r="A574" s="4">
         <v>45940</v>
       </c>
@@ -32716,7 +32715,7 @@
         <v>2.0950000000000002</v>
       </c>
     </row>
-    <row r="575" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:18">
       <c r="A575" s="4">
         <v>45943</v>
       </c>
@@ -32772,7 +32771,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="576" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:18">
       <c r="A576" s="4">
         <v>45944</v>
       </c>
@@ -32828,7 +32827,7 @@
         <v>2.0550000000000002</v>
       </c>
     </row>
-    <row r="577" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:18">
       <c r="A577" s="4">
         <v>45945</v>
       </c>
@@ -32884,7 +32883,7 @@
         <v>2.0750000000000002</v>
       </c>
     </row>
-    <row r="578" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:18">
       <c r="A578" s="4">
         <v>45946</v>
       </c>
@@ -32940,7 +32939,7 @@
         <v>2.1349999999999998</v>
       </c>
     </row>
-    <row r="579" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:18">
       <c r="A579" s="4">
         <v>45947</v>
       </c>
@@ -32996,7 +32995,7 @@
         <v>2.105</v>
       </c>
     </row>
-    <row r="580" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:18">
       <c r="A580" s="4">
         <v>45950</v>
       </c>
@@ -33052,7 +33051,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="581" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:18">
       <c r="A581" s="4">
         <v>45951</v>
       </c>
@@ -33108,7 +33107,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="582" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:18">
       <c r="A582" s="4">
         <v>45952</v>
       </c>
@@ -33164,7 +33163,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="583" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:18">
       <c r="A583" s="4">
         <v>45953</v>
       </c>
@@ -33220,7 +33219,7 @@
         <v>2.1749999999999998</v>
       </c>
     </row>
-    <row r="584" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:18">
       <c r="A584" s="4">
         <v>45954</v>
       </c>
@@ -33276,7 +33275,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="585" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:18">
       <c r="A585" s="4">
         <v>45957</v>
       </c>
@@ -33332,7 +33331,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="586" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:18">
       <c r="A586" s="4">
         <v>45958</v>
       </c>
@@ -33388,7 +33387,7 @@
         <v>2.1749999999999998</v>
       </c>
     </row>
-    <row r="587" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:18">
       <c r="A587" s="4">
         <v>45959</v>
       </c>
@@ -33444,7 +33443,7 @@
         <v>2.2349999999999999</v>
       </c>
     </row>
-    <row r="588" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:18">
       <c r="A588" s="4">
         <v>45960</v>
       </c>
@@ -33500,7 +33499,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="589" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:18">
       <c r="A589" s="4">
         <v>45961</v>
       </c>
@@ -33556,7 +33555,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="590" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:18">
       <c r="A590" s="4">
         <v>45964</v>
       </c>
@@ -33612,7 +33611,7 @@
         <v>2.3050000000000002</v>
       </c>
     </row>
-    <row r="591" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:18">
       <c r="A591" s="4">
         <v>45965</v>
       </c>
@@ -33668,7 +33667,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="592" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:18">
       <c r="A592" s="4">
         <v>45966</v>
       </c>
@@ -33724,7 +33723,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="593" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:18">
       <c r="A593" s="4">
         <v>45967</v>
       </c>
@@ -33780,7 +33779,7 @@
         <v>2.3650000000000002</v>
       </c>
     </row>
-    <row r="594" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:18">
       <c r="A594" s="4">
         <v>45968</v>
       </c>
@@ -33836,7 +33835,7 @@
         <v>2.4249999999999998</v>
       </c>
     </row>
-    <row r="595" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:18">
       <c r="A595" s="4">
         <v>45971</v>
       </c>
@@ -33892,7 +33891,7 @@
         <v>2.4849999999999999</v>
       </c>
     </row>
-    <row r="596" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:18">
       <c r="A596" s="4">
         <v>45972</v>
       </c>
@@ -33948,7 +33947,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="597" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:18">
       <c r="A597" s="4">
         <v>45973</v>
       </c>
@@ -34004,7 +34003,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="598" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:18">
       <c r="A598" s="4">
         <v>45974</v>
       </c>
@@ -34060,7 +34059,7 @@
         <v>2.5150000000000001</v>
       </c>
     </row>
-    <row r="599" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:18">
       <c r="A599" s="4">
         <v>45975</v>
       </c>
@@ -34116,7 +34115,7 @@
         <v>2.585</v>
       </c>
     </row>
-    <row r="600" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:18">
       <c r="A600" s="4">
         <v>45978</v>
       </c>
@@ -34172,7 +34171,7 @@
         <v>2.5950000000000002</v>
       </c>
     </row>
-    <row r="601" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:18">
       <c r="A601" s="4">
         <v>45979</v>
       </c>
@@ -34228,7 +34227,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="602" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:18">
       <c r="A602" s="4">
         <v>45980</v>
       </c>
@@ -34284,7 +34283,7 @@
         <v>2.605</v>
       </c>
     </row>
-    <row r="603" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:18">
       <c r="A603" s="4">
         <v>45981</v>
       </c>
@@ -34340,7 +34339,7 @@
         <v>2.6349999999999998</v>
       </c>
     </row>
-    <row r="604" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:18">
       <c r="A604" s="4">
         <v>45982</v>
       </c>
@@ -34396,7 +34395,7 @@
         <v>2.6150000000000002</v>
       </c>
     </row>
-    <row r="605" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:18">
       <c r="A605" s="4">
         <v>45985</v>
       </c>
@@ -34452,7 +34451,7 @@
         <v>2.6549999999999998</v>
       </c>
     </row>
-    <row r="606" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:18">
       <c r="A606" s="4">
         <v>45986</v>
       </c>
@@ -34508,7 +34507,7 @@
         <v>2.6549999999999998</v>
       </c>
     </row>
-    <row r="607" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:18">
       <c r="A607" s="4">
         <v>45987</v>
       </c>
@@ -34564,7 +34563,7 @@
         <v>2.645</v>
       </c>
     </row>
-    <row r="608" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:18">
       <c r="A608" s="4">
         <v>45988</v>
       </c>
@@ -34620,7 +34619,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="609" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:18">
       <c r="A609" s="4">
         <v>45989</v>
       </c>
@@ -34676,7 +34675,7 @@
         <v>2.645</v>
       </c>
     </row>
-    <row r="610" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:18">
       <c r="A610" s="4">
         <v>45992</v>
       </c>
@@ -34732,7 +34731,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="611" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:18">
       <c r="A611" s="4">
         <v>45993</v>
       </c>
@@ -34788,7 +34787,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="612" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:18">
       <c r="A612" s="4">
         <v>45994</v>
       </c>
@@ -34844,7 +34843,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="613" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:18">
       <c r="A613" s="4">
         <v>45995</v>
       </c>
@@ -34900,7 +34899,7 @@
         <v>2.7250000000000001</v>
       </c>
     </row>
-    <row r="614" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:18">
       <c r="A614" s="4">
         <v>45996</v>
       </c>
@@ -34956,7 +34955,7 @@
         <v>2.6949999999999998</v>
       </c>
     </row>
-    <row r="615" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:18">
       <c r="A615" s="4">
         <v>45999</v>
       </c>
@@ -35012,7 +35011,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="616" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:18">
       <c r="A616" s="4">
         <v>46000</v>
       </c>
@@ -35068,7 +35067,7 @@
         <v>2.7949999999999999</v>
       </c>
     </row>
-    <row r="617" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:18">
       <c r="A617" s="4">
         <v>46001</v>
       </c>
@@ -35124,7 +35123,7 @@
         <v>2.8149999999999999</v>
       </c>
     </row>
-    <row r="618" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:18">
       <c r="A618" s="4">
         <v>46002</v>
       </c>
@@ -35180,7 +35179,7 @@
         <v>2.8050000000000002</v>
       </c>
     </row>
-    <row r="619" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:18">
       <c r="A619" s="4">
         <v>46003</v>
       </c>
@@ -35236,7 +35235,7 @@
         <v>2.7949999999999999</v>
       </c>
     </row>
-    <row r="620" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:18">
       <c r="A620" s="4">
         <v>46006</v>
       </c>
@@ -35292,7 +35291,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="621" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:18">
       <c r="A621" s="4">
         <v>46007</v>
       </c>
@@ -35348,7 +35347,7 @@
         <v>2.7349999999999999</v>
       </c>
     </row>
-    <row r="622" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:18">
       <c r="A622" s="4">
         <v>46008</v>
       </c>
@@ -35404,7 +35403,7 @@
         <v>2.7050000000000001</v>
       </c>
     </row>
-    <row r="623" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:18">
       <c r="A623" s="4">
         <v>46009</v>
       </c>
@@ -35460,7 +35459,7 @@
         <v>2.665</v>
       </c>
     </row>
-    <row r="624" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:18">
       <c r="A624" s="4">
         <v>46010</v>
       </c>
@@ -35516,7 +35515,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="625" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:18">
       <c r="A625" s="4">
         <v>46013</v>
       </c>
@@ -35572,7 +35571,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="626" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:18">
       <c r="A626" s="4">
         <v>46014</v>
       </c>
@@ -35628,7 +35627,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="627" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:18">
       <c r="A627" s="4">
         <v>46015</v>
       </c>
@@ -35684,7 +35683,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="628" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:18">
       <c r="A628" s="4">
         <v>46017</v>
       </c>
@@ -35740,7 +35739,7 @@
         <v>2.6949999999999998</v>
       </c>
     </row>
-    <row r="629" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:18">
       <c r="A629" s="4">
         <v>46020</v>
       </c>
@@ -35796,7 +35795,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="630" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:18">
       <c r="A630" s="4">
         <v>46021</v>
       </c>
@@ -35852,7 +35851,7 @@
         <v>2.7749999999999999</v>
       </c>
     </row>
-    <row r="631" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:18">
       <c r="A631" s="4">
         <v>46022</v>
       </c>
@@ -35908,7 +35907,7 @@
         <v>2.7749999999999999</v>
       </c>
     </row>
-    <row r="632" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:18">
       <c r="A632" s="4">
         <v>46024</v>
       </c>
@@ -35964,7 +35963,7 @@
         <v>2.7749999999999999</v>
       </c>
     </row>
-    <row r="633" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:18">
       <c r="A633" s="4">
         <v>46027</v>
       </c>
@@ -36020,7 +36019,7 @@
         <v>2.8250000000000002</v>
       </c>
     </row>
-    <row r="634" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:18">
       <c r="A634" s="4">
         <v>46028</v>
       </c>
@@ -36076,7 +36075,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="635" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:18">
       <c r="A635" s="4">
         <v>46029</v>
       </c>
@@ -36132,7 +36131,7 @@
         <v>2.855</v>
       </c>
     </row>
-    <row r="636" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:18">
       <c r="A636" s="4">
         <v>46030</v>
       </c>
@@ -36188,7 +36187,7 @@
         <v>2.8650000000000002</v>
       </c>
     </row>
-    <row r="637" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:18">
       <c r="A637" s="4">
         <v>46031</v>
       </c>
@@ -36244,7 +36243,7 @@
         <v>2.915</v>
       </c>
     </row>
-    <row r="638" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:18">
       <c r="A638" s="4">
         <v>46034</v>
       </c>
@@ -36300,7 +36299,7 @@
         <v>2.9449999999999998</v>
       </c>
     </row>
-    <row r="639" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:18">
       <c r="A639" s="4">
         <v>46035</v>
       </c>
@@ -36356,7 +36355,7 @@
         <v>2.9249999999999998</v>
       </c>
     </row>
-    <row r="640" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:18">
       <c r="A640" s="4">
         <v>46036</v>
       </c>
@@ -36412,7 +36411,7 @@
         <v>2.8650000000000002</v>
       </c>
     </row>
-    <row r="641" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:18">
       <c r="A641" s="4">
         <v>46037</v>
       </c>
@@ -36468,7 +36467,7 @@
         <v>2.9049999999999998</v>
       </c>
     </row>
-    <row r="642" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:18">
       <c r="A642" s="4">
         <v>46038</v>
       </c>
@@ -36524,7 +36523,7 @@
         <v>2.895</v>
       </c>
     </row>
-    <row r="643" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:18">
       <c r="A643" s="4">
         <v>46041</v>
       </c>
@@ -36580,7 +36579,7 @@
         <v>2.9449999999999998</v>
       </c>
     </row>
-    <row r="644" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:18">
       <c r="A644" s="4">
         <v>46042</v>
       </c>
@@ -36636,7 +36635,7 @@
         <v>2.9950000000000001</v>
       </c>
     </row>
-    <row r="645" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:18">
       <c r="A645" s="4">
         <v>46043</v>
       </c>
@@ -36692,7 +36691,7 @@
         <v>2.9049999999999998</v>
       </c>
     </row>
-    <row r="646" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:18">
       <c r="A646" s="4">
         <v>46044</v>
       </c>
@@ -36748,7 +36747,7 @@
         <v>2.875</v>
       </c>
     </row>
-    <row r="647" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:18">
       <c r="A647" s="4">
         <v>46045</v>
       </c>
@@ -36804,7 +36803,7 @@
         <v>2.915</v>
       </c>
     </row>
-    <row r="648" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:18">
       <c r="A648" s="4">
         <v>46048</v>
       </c>
@@ -36860,7 +36859,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="649" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:18">
       <c r="A649" s="4">
         <v>46049</v>
       </c>
@@ -36916,7 +36915,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="650" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:18">
       <c r="A650" s="4">
         <v>46050</v>
       </c>
@@ -36972,7 +36971,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="651" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:18">
       <c r="A651" s="4">
         <v>46051</v>
       </c>
@@ -37028,7 +37027,7 @@
         <v>2.895</v>
       </c>
     </row>
-    <row r="652" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:18">
       <c r="A652" s="4">
         <v>46052</v>
       </c>
@@ -37084,7 +37083,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="653" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:18">
       <c r="A653" s="4">
         <v>46055</v>
       </c>
@@ -37140,7 +37139,7 @@
         <v>2.9449999999999998</v>
       </c>
     </row>
-    <row r="654" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:18">
       <c r="A654" s="4">
         <v>46056</v>
       </c>
@@ -37196,7 +37195,7 @@
         <v>3.0049999999999999</v>
       </c>
     </row>
-    <row r="655" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:18">
       <c r="A655" s="4">
         <v>46057</v>
       </c>
@@ -37252,7 +37251,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="656" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:18">
       <c r="A656" s="4">
         <v>46058</v>
       </c>
@@ -37308,7 +37307,7 @@
         <v>3.0550000000000002</v>
       </c>
     </row>
-    <row r="657" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:18">
       <c r="A657" s="4">
         <v>46059</v>
       </c>
@@ -37364,7 +37363,7 @@
         <v>3.0750000000000002</v>
       </c>
     </row>
-    <row r="658" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:18">
       <c r="A658" s="4">
         <v>46062</v>
       </c>
@@ -37420,7 +37419,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="659" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:18">
       <c r="A659" s="4">
         <v>46063</v>
       </c>
@@ -37476,7 +37475,7 @@
         <v>3.0449999999999999</v>
       </c>
     </row>
-    <row r="660" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:18">
       <c r="A660" s="4">
         <v>46064</v>
       </c>
@@ -37532,7 +37531,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="661" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:18">
       <c r="A661" s="4">
         <v>46065</v>
       </c>
@@ -37588,7 +37587,7 @@
         <v>3.0049999999999999</v>
       </c>
     </row>
-    <row r="662" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:18">
       <c r="A662" s="4">
         <v>46066</v>
       </c>
@@ -37644,7 +37643,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="663" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:18">
       <c r="A663" s="4">
         <v>46072</v>
       </c>
@@ -37700,7 +37699,7 @@
         <v>2.9550000000000001</v>
       </c>
     </row>
-    <row r="664" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:18">
       <c r="A664" s="4">
         <v>46073</v>
       </c>
@@ -37756,7 +37755,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="665" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:18">
       <c r="A665" s="4">
         <v>46076</v>
       </c>
@@ -37812,7 +37811,7 @@
         <v>2.9750000000000001</v>
       </c>
     </row>
-    <row r="666" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:18">
       <c r="A666" s="4">
         <v>46077</v>
       </c>
@@ -37868,7 +37867,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="667" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:18">
       <c r="A667" s="4">
         <v>46078</v>
       </c>
@@ -37924,7 +37923,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="668" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:18">
       <c r="A668" s="4">
         <v>46079</v>
       </c>
@@ -37980,7 +37979,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="669" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:18">
       <c r="A669" s="4">
         <v>46080</v>
       </c>
@@ -38036,7 +38035,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="670" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:18">
       <c r="A670" s="4">
         <v>46084</v>
       </c>
@@ -38092,7 +38091,7 @@
         <v>2.9750000000000001</v>
       </c>
     </row>
-    <row r="671" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:18">
       <c r="A671" s="4">
         <v>46085</v>
       </c>
@@ -38148,7 +38147,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="672" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:18">
       <c r="A672" s="4">
         <v>46086</v>
       </c>
@@ -38204,7 +38203,7 @@
         <v>3.0150000000000001</v>
       </c>
     </row>
-    <row r="673" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:18">
       <c r="A673" s="4">
         <v>46087</v>
       </c>
@@ -38260,7 +38259,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="674" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:18">
       <c r="A674" s="4">
         <v>46090</v>
       </c>
@@ -38316,7 +38315,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="675" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:18">
       <c r="A675" s="4">
         <v>46091</v>
       </c>
@@ -38372,7 +38371,7 @@
         <v>2.9849999999999999</v>
       </c>
     </row>
-    <row r="676" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:18">
       <c r="A676" s="4">
         <v>46092</v>
       </c>
@@ -38428,7 +38427,7 @@
         <v>2.9750000000000001</v>
       </c>
     </row>
-    <row r="677" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:18">
       <c r="A677" s="4">
         <v>46093</v>
       </c>
@@ -38484,7 +38483,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="678" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:18">
       <c r="A678" s="4">
         <v>46094</v>
       </c>
@@ -38540,7 +38539,7 @@
         <v>3.085</v>
       </c>
     </row>
-    <row r="679" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:18">
       <c r="A679" s="4">
         <v>46097</v>
       </c>
@@ -38596,7 +38595,7 @@
         <v>3.0649999999999999</v>
       </c>
     </row>
-    <row r="680" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:18">
       <c r="A680" s="4">
         <v>46098</v>
       </c>
@@ -38652,7 +38651,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="681" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:18">
       <c r="A681" s="4">
         <v>46099</v>
       </c>
@@ -38708,7 +38707,7 @@
         <v>3.0750000000000002</v>
       </c>
     </row>
-    <row r="682" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:18">
       <c r="A682" s="4">
         <v>46100</v>
       </c>
@@ -38764,7 +38763,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="683" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:18">
       <c r="A683" s="4">
         <v>46101</v>
       </c>
@@ -38820,7 +38819,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="684" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:18">
       <c r="A684" s="4">
         <v>46104</v>
       </c>
@@ -38876,7 +38875,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="685" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:18">
       <c r="A685" s="4">
         <v>46105</v>
       </c>
@@ -38932,7 +38931,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="686" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:18">
       <c r="A686" s="4">
         <v>46106</v>
       </c>
@@ -38988,7 +38987,7 @@
         <v>3.2850000000000001</v>
       </c>
     </row>
-    <row r="687" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:18">
       <c r="A687" s="4">
         <v>46107</v>
       </c>
@@ -39044,7 +39043,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="688" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:18">
       <c r="A688" s="4">
         <v>46108</v>
       </c>
@@ -39100,7 +39099,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="689" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:18">
       <c r="A689" s="4">
         <v>46111</v>
       </c>
@@ -39156,7 +39155,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="690" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:18">
       <c r="A690" s="4">
         <v>46112</v>
       </c>
@@ -39212,7 +39211,7 @@
         <v>3.2349999999999999</v>
       </c>
     </row>
-    <row r="691" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:18">
       <c r="A691" s="4">
         <v>46113</v>
       </c>
@@ -39268,7 +39267,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="692" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:18">
       <c r="A692" s="4">
         <v>46114</v>
       </c>
@@ -39324,7 +39323,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="693" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:18">
       <c r="A693" s="4">
         <v>46115</v>
       </c>
@@ -39380,7 +39379,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="694" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:18">
       <c r="A694" s="4">
         <v>46118</v>
       </c>
@@ -39436,7 +39435,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="695" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:18">
       <c r="A695" s="4">
         <v>46119</v>
       </c>
@@ -39492,7 +39491,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="696" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:18">
       <c r="A696" s="4">
         <v>46120</v>
       </c>
@@ -39548,7 +39547,7 @@
         <v>2.9249999999999998</v>
       </c>
     </row>
-    <row r="697" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:18">
       <c r="A697" s="4">
         <v>46121</v>
       </c>
@@ -39604,7 +39603,7 @@
         <v>2.9249999999999998</v>
       </c>
     </row>
-    <row r="698" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:18">
       <c r="A698" s="4">
         <v>46122</v>
       </c>
@@ -39660,7 +39659,7 @@
         <v>2.9350000000000001</v>
       </c>
     </row>
-    <row r="699" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:18">
       <c r="A699" s="4">
         <v>46125</v>
       </c>
@@ -39716,7 +39715,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="700" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:18">
       <c r="A700" s="4">
         <v>46126</v>
       </c>
@@ -39772,7 +39771,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="701" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:18">
       <c r="A701" s="4">
         <v>46127</v>
       </c>
@@ -39828,7 +39827,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="702" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:18">
       <c r="A702" s="4">
         <v>46128</v>
       </c>
@@ -39884,7 +39883,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="703" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:18">
       <c r="A703" s="4">
         <v>46129</v>
       </c>
@@ -39940,7 +39939,7 @@
         <v>2.9350000000000001</v>
       </c>
     </row>
-    <row r="704" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:18">
       <c r="A704" s="4">
         <v>46132</v>
       </c>
@@ -39996,7 +39995,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="705" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:18">
       <c r="A705" s="4">
         <v>46133</v>
       </c>
@@ -40052,7 +40051,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="706" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:18">
       <c r="A706" s="4">
         <v>46134</v>
       </c>
@@ -40108,7 +40107,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="707" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:18">
       <c r="A707" s="4">
         <v>46135</v>
       </c>
@@ -40164,7 +40163,7 @@
         <v>3.0249999999999999</v>
       </c>
     </row>
-    <row r="708" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:18">
       <c r="A708" s="4">
         <v>46136</v>
       </c>
@@ -40220,7 +40219,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="709" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:18">
       <c r="A709" s="4">
         <v>46139</v>
       </c>
@@ -40276,7 +40275,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="710" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:18">
       <c r="A710" s="4">
         <v>46140</v>
       </c>
@@ -40332,7 +40331,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="711" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:18">
       <c r="A711" s="4">
         <v>46141</v>
       </c>
@@ -40388,7 +40387,7 @@
         <v>3.2050000000000001</v>
       </c>
     </row>
-    <row r="712" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:18">
       <c r="A712" s="4">
         <v>46142</v>
       </c>
@@ -40444,7 +40443,7 @@
         <v>3.2450000000000001</v>
       </c>
     </row>
-    <row r="713" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:18">
       <c r="A713" s="4">
         <v>46146</v>
       </c>
@@ -40500,7 +40499,7 @@
         <v>3.2549999999999999</v>
       </c>
     </row>
-    <row r="714" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:18">
       <c r="A714" s="4">
         <v>46148</v>
       </c>
@@ -40556,7 +40555,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="715" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:18">
       <c r="A715" s="4">
         <v>46149</v>
       </c>
@@ -40612,7 +40611,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="716" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:18">
       <c r="A716" s="4">
         <v>46150</v>
       </c>
@@ -40668,7 +40667,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="717" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:18">
       <c r="A717" s="4">
         <v>46153</v>
       </c>
@@ -40724,7 +40723,7 @@
         <v>3.1349999999999998</v>
       </c>
     </row>
-    <row r="718" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:18">
       <c r="A718" s="4">
         <v>46154</v>
       </c>
@@ -40780,7 +40779,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="719" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:18">
       <c r="A719" s="4">
         <v>46155</v>
       </c>
@@ -40836,7 +40835,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="720" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:18">
       <c r="A720" s="4">
         <v>46156</v>
       </c>
@@ -40892,7 +40891,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="721" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:18">
       <c r="A721" s="4">
         <v>46157</v>
       </c>
@@ -40948,7 +40947,7 @@
         <v>3.2349999999999999</v>
       </c>
     </row>
-    <row r="722" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:18">
       <c r="A722" s="4">
         <v>46160</v>
       </c>
@@ -41004,7 +41003,7 @@
         <v>3.2850000000000001</v>
       </c>
     </row>
-    <row r="723" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:18">
       <c r="A723" s="4">
         <v>46161</v>
       </c>
@@ -41060,7 +41059,7 @@
         <v>3.3050000000000002</v>
       </c>
     </row>
-    <row r="724" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:18">
       <c r="A724" s="4">
         <v>46162</v>
       </c>
@@ -41116,7 +41115,7 @@
         <v>3.3149999999999999</v>
       </c>
     </row>
-    <row r="725" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:18">
       <c r="A725" s="4">
         <v>46163</v>
       </c>
@@ -41172,7 +41171,7 @@
         <v>3.3149999999999999</v>
       </c>
     </row>
-    <row r="726" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:18">
       <c r="A726" s="4">
         <v>46164</v>
       </c>
@@ -41228,7 +41227,7 @@
         <v>3.2850000000000001</v>
       </c>
     </row>
-    <row r="727" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:18">
       <c r="A727" s="4">
         <v>46168</v>
       </c>
@@ -41284,7 +41283,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="728" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:18">
       <c r="A728" s="4">
         <v>46169</v>
       </c>
@@ -41340,7 +41339,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="729" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:18">
       <c r="A729" s="4">
         <v>46170</v>
       </c>
@@ -41396,7 +41395,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="730" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:18">
       <c r="A730" s="4">
         <v>46171</v>
       </c>
@@ -41452,7 +41451,7 @@
         <v>3.2250000000000001</v>
       </c>
     </row>
-    <row r="731" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:18">
       <c r="A731" s="4">
         <v>46174</v>
       </c>
@@ -41508,7 +41507,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="732" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:18">
       <c r="A732" s="4">
         <v>46175</v>
       </c>
@@ -41564,7 +41563,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="733" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:18">
       <c r="A733" s="4">
         <v>46177</v>
       </c>
@@ -41620,7 +41619,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="734" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:18">
       <c r="A734" s="4">
         <v>46178</v>
       </c>
@@ -41676,7 +41675,7 @@
         <v>3.415</v>
       </c>
     </row>
-    <row r="735" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:18">
       <c r="A735" s="4">
         <v>46181</v>
       </c>
@@ -41732,7 +41731,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="736" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:18">
       <c r="A736" s="4">
         <v>46182</v>
       </c>
@@ -41788,7 +41787,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="737" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:18">
       <c r="A737" s="4">
         <v>46183</v>
       </c>
@@ -41844,7 +41843,7 @@
         <v>3.415</v>
       </c>
     </row>
-    <row r="738" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:18">
       <c r="A738" s="4">
         <v>46184</v>
       </c>
@@ -41900,7 +41899,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="739" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:18">
       <c r="A739" s="4">
         <v>46185</v>
       </c>
@@ -41956,7 +41955,7 @@
         <v>3.3450000000000002</v>
       </c>
     </row>
-    <row r="740" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:18">
       <c r="A740" s="4">
         <v>46188</v>
       </c>
@@ -42012,7 +42011,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="741" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:18">
       <c r="A741" s="4">
         <v>46189</v>
       </c>
@@ -42068,7 +42067,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="742" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:18">
       <c r="A742" s="4">
         <v>46190</v>
       </c>
@@ -42124,7 +42123,7 @@
         <v>3.2450000000000001</v>
       </c>
     </row>
-    <row r="743" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:18">
       <c r="A743" s="4">
         <v>46191</v>
       </c>
@@ -42180,7 +42179,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="744" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:18">
       <c r="A744" s="4">
         <v>46192</v>
       </c>
@@ -42236,7 +42235,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="745" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:18">
       <c r="A745" s="4">
         <v>46195</v>
       </c>
@@ -42292,7 +42291,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="746" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:18">
       <c r="A746" s="4">
         <v>46196</v>
       </c>
@@ -42348,7 +42347,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="747" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:18">
       <c r="A747" s="4">
         <v>46197</v>
       </c>
@@ -42404,7 +42403,7 @@
         <v>3.3650000000000002</v>
       </c>
     </row>
-    <row r="748" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:18">
       <c r="A748" s="4">
         <v>46198</v>
       </c>
@@ -42460,7 +42459,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="749" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:18">
       <c r="A749" s="4">
         <v>46199</v>
       </c>
@@ -42516,7 +42515,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="750" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:18">
       <c r="A750" s="4">
         <v>46202</v>
       </c>
@@ -42572,7 +42571,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="751" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:18">
       <c r="A751" s="4">
         <v>46203</v>
       </c>
@@ -42628,7 +42627,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="752" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:18">
       <c r="A752" s="4">
         <v>46204</v>
       </c>
@@ -42684,7 +42683,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="753" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:18">
       <c r="A753" s="4">
         <v>46205</v>
       </c>
@@ -42740,7 +42739,7 @@
         <v>3.4449999999999998</v>
       </c>
     </row>
-    <row r="754" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:18">
       <c r="A754" s="4">
         <v>46206</v>
       </c>
@@ -42796,7 +42795,7 @@
         <v>3.4649999999999999</v>
       </c>
     </row>
-    <row r="755" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:18">
       <c r="A755" s="4">
         <v>46209</v>
       </c>
@@ -42852,7 +42851,7 @@
         <v>3.4649999999999999</v>
       </c>
     </row>
-    <row r="756" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:18">
       <c r="A756" s="4">
         <v>46210</v>
       </c>
@@ -42908,7 +42907,7 @@
         <v>3.4249999999999998</v>
       </c>
     </row>
-    <row r="757" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:18">
       <c r="A757" s="4">
         <v>46211</v>
       </c>
@@ -42964,7 +42963,7 @@
         <v>3.415</v>
       </c>
     </row>
-    <row r="758" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:18">
       <c r="A758" s="4">
         <v>46212</v>
       </c>
@@ -43020,7 +43019,7 @@
         <v>3.4249999999999998</v>
       </c>
     </row>
-    <row r="759" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:18">
       <c r="A759" s="4">
         <v>46213</v>
       </c>
@@ -43076,7 +43075,7 @@
         <v>3.4249999999999998</v>
       </c>
     </row>
-    <row r="760" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:18">
       <c r="A760" s="4">
         <v>46216</v>
       </c>
@@ -43132,7 +43131,7 @@
         <v>3.4649999999999999</v>
       </c>
     </row>
-    <row r="761" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:18">
       <c r="A761" s="4">
         <v>46217</v>
       </c>
@@ -43188,7 +43187,7 @@
         <v>3.5049999999999999</v>
       </c>
     </row>
-    <row r="762" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:18">
       <c r="A762" s="4">
         <v>46218</v>
       </c>
@@ -43244,7 +43243,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="763" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:18">
       <c r="A763" s="4">
         <v>46219</v>
       </c>
@@ -43300,7 +43299,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="764" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:18">
       <c r="A764" s="4">
         <v>46223</v>
       </c>
@@ -43356,7 +43355,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="765" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:18">
       <c r="A765" s="4">
         <v>46224</v>
       </c>
@@ -43412,7 +43411,7 @@
         <v>3.5249999999999999</v>
       </c>
     </row>
-    <row r="766" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:18">
       <c r="A766" s="4">
         <v>46225</v>
       </c>
@@ -43468,7 +43467,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="767" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:18">
       <c r="A767" s="4">
         <v>46226</v>
       </c>
@@ -43524,7 +43523,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="768" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:18">
       <c r="A768" s="4">
         <v>46227</v>
       </c>
@@ -43580,7 +43579,7 @@
         <v>3.625</v>
       </c>
     </row>
-    <row r="769" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:18">
       <c r="A769" s="4">
         <v>46230</v>
       </c>
@@ -43636,7 +43635,7 @@
         <v>3.5249999999999999</v>
       </c>
     </row>
-    <row r="770" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:18">
       <c r="A770" s="4">
         <v>46231</v>
       </c>
@@ -43692,7 +43691,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="771" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:18">
       <c r="A771" s="4">
         <v>46232</v>
       </c>
@@ -43748,7 +43747,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="772" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:18">
       <c r="A772" s="4">
         <v>46233</v>
       </c>
@@ -43802,6 +43801,622 @@
       </c>
       <c r="R772" s="9">
         <v>3.5350000000000001</v>
+      </c>
+    </row>
+    <row r="773" spans="1:18">
+      <c r="A773" s="4">
+        <v>46234</v>
+      </c>
+      <c r="B773" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C773" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D773" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E773" s="2">
+        <v>3.4125000000000001</v>
+      </c>
+      <c r="F773" s="2">
+        <v>3.7124999999999999</v>
+      </c>
+      <c r="G773" s="2">
+        <v>3.8374999999999999</v>
+      </c>
+      <c r="H773" s="2">
+        <v>3.91</v>
+      </c>
+      <c r="I773" s="2">
+        <v>3.96</v>
+      </c>
+      <c r="J773" s="2">
+        <v>4.03</v>
+      </c>
+      <c r="K773" s="2">
+        <v>4.0925000000000002</v>
+      </c>
+      <c r="L773" s="9">
+        <v>3.4125000000000001</v>
+      </c>
+      <c r="M773" s="9">
+        <v>3.7124999999999999</v>
+      </c>
+      <c r="N773" s="9">
+        <v>3.8374999999999999</v>
+      </c>
+      <c r="O773" s="9">
+        <v>3.91</v>
+      </c>
+      <c r="P773" s="9">
+        <v>3.96</v>
+      </c>
+      <c r="Q773" s="9">
+        <v>4.03</v>
+      </c>
+      <c r="R773" s="9">
+        <v>4.0925000000000002</v>
+      </c>
+    </row>
+    <row r="774" spans="1:18">
+      <c r="A774" s="4">
+        <v>46237</v>
+      </c>
+      <c r="B774" s="4">
+        <v>46237</v>
+      </c>
+      <c r="C774" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D774" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E774" s="2">
+        <v>3.4125000000000001</v>
+      </c>
+      <c r="F774" s="2">
+        <v>3.7124999999999999</v>
+      </c>
+      <c r="G774" s="2">
+        <v>3.8374999999999999</v>
+      </c>
+      <c r="H774" s="2">
+        <v>3.91</v>
+      </c>
+      <c r="I774" s="2">
+        <v>3.96</v>
+      </c>
+      <c r="J774" s="2">
+        <v>4.03</v>
+      </c>
+      <c r="K774" s="2">
+        <v>4.0925000000000002</v>
+      </c>
+      <c r="L774" s="9">
+        <v>3.3925000000000001</v>
+      </c>
+      <c r="M774" s="9">
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="N774" s="9">
+        <v>3.8050000000000002</v>
+      </c>
+      <c r="O774" s="9">
+        <v>3.8824999999999998</v>
+      </c>
+      <c r="P774" s="9">
+        <v>3.9350000000000001</v>
+      </c>
+      <c r="Q774" s="9">
+        <v>4.01</v>
+      </c>
+      <c r="R774" s="9">
+        <v>4.0750000000000002</v>
+      </c>
+    </row>
+    <row r="775" spans="1:18">
+      <c r="A775" s="4">
+        <v>46238</v>
+      </c>
+      <c r="B775" s="4">
+        <v>46238</v>
+      </c>
+      <c r="C775" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D775" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E775" s="2">
+        <v>3.3925000000000001</v>
+      </c>
+      <c r="F775" s="2">
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="G775" s="2">
+        <v>3.8050000000000002</v>
+      </c>
+      <c r="H775" s="2">
+        <v>3.8824999999999998</v>
+      </c>
+      <c r="I775" s="2">
+        <v>3.9350000000000001</v>
+      </c>
+      <c r="J775" s="2">
+        <v>4.01</v>
+      </c>
+      <c r="K775" s="2">
+        <v>4.0750000000000002</v>
+      </c>
+      <c r="L775" s="9">
+        <v>3.3774999999999999</v>
+      </c>
+      <c r="M775" s="9">
+        <v>3.6625000000000001</v>
+      </c>
+      <c r="N775" s="9">
+        <v>3.7825000000000002</v>
+      </c>
+      <c r="O775" s="9">
+        <v>3.855</v>
+      </c>
+      <c r="P775" s="9">
+        <v>3.91</v>
+      </c>
+      <c r="Q775" s="9">
+        <v>3.98</v>
+      </c>
+      <c r="R775" s="9">
+        <v>4.0425000000000004</v>
+      </c>
+    </row>
+    <row r="776" spans="1:18">
+      <c r="A776" s="4">
+        <v>46239</v>
+      </c>
+      <c r="B776" s="4">
+        <v>46239</v>
+      </c>
+      <c r="C776" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D776" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E776" s="2">
+        <v>3.3774999999999999</v>
+      </c>
+      <c r="F776" s="2">
+        <v>3.6625000000000001</v>
+      </c>
+      <c r="G776" s="2">
+        <v>3.7825000000000002</v>
+      </c>
+      <c r="H776" s="2">
+        <v>3.855</v>
+      </c>
+      <c r="I776" s="2">
+        <v>3.91</v>
+      </c>
+      <c r="J776" s="2">
+        <v>3.98</v>
+      </c>
+      <c r="K776" s="2">
+        <v>4.0425000000000004</v>
+      </c>
+      <c r="L776" s="9">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="M776" s="9">
+        <v>3.62</v>
+      </c>
+      <c r="N776" s="9">
+        <v>3.7250000000000001</v>
+      </c>
+      <c r="O776" s="9">
+        <v>3.7850000000000001</v>
+      </c>
+      <c r="P776" s="9">
+        <v>3.8325</v>
+      </c>
+      <c r="Q776" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="R776" s="9">
+        <v>3.9525000000000001</v>
+      </c>
+    </row>
+    <row r="777" spans="1:18">
+      <c r="A777" s="4">
+        <v>46240</v>
+      </c>
+      <c r="B777" s="4">
+        <v>46240</v>
+      </c>
+      <c r="C777" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D777" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E777" s="2">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="F777" s="2">
+        <v>3.62</v>
+      </c>
+      <c r="G777" s="2">
+        <v>3.7250000000000001</v>
+      </c>
+      <c r="H777" s="2">
+        <v>3.7850000000000001</v>
+      </c>
+      <c r="I777" s="2">
+        <v>3.8325</v>
+      </c>
+      <c r="J777" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="K777" s="2">
+        <v>3.9525000000000001</v>
+      </c>
+      <c r="L777" s="9">
+        <v>3.4125000000000001</v>
+      </c>
+      <c r="M777" s="9">
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="N777" s="9">
+        <v>3.7825000000000002</v>
+      </c>
+      <c r="O777" s="9">
+        <v>3.84</v>
+      </c>
+      <c r="P777" s="9">
+        <v>3.8875000000000002</v>
+      </c>
+      <c r="Q777" s="9">
+        <v>3.9449999999999998</v>
+      </c>
+      <c r="R777" s="9">
+        <v>3.9950000000000001</v>
+      </c>
+    </row>
+    <row r="778" spans="1:18">
+      <c r="A778" s="4">
+        <v>46241</v>
+      </c>
+      <c r="B778" s="4">
+        <v>46241</v>
+      </c>
+      <c r="C778" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D778" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E778" s="2">
+        <v>3.43</v>
+      </c>
+      <c r="F778" s="2">
+        <v>3.69</v>
+      </c>
+      <c r="G778" s="2">
+        <v>3.79</v>
+      </c>
+      <c r="H778" s="2">
+        <v>3.8574999999999999</v>
+      </c>
+      <c r="I778" s="2">
+        <v>3.9049999999999998</v>
+      </c>
+      <c r="J778" s="2">
+        <v>3.9649999999999999</v>
+      </c>
+      <c r="K778" s="2">
+        <v>4.0149999999999997</v>
+      </c>
+      <c r="L778" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="M778" s="9">
+        <v>3.69</v>
+      </c>
+      <c r="N778" s="9">
+        <v>3.79</v>
+      </c>
+      <c r="O778" s="9">
+        <v>3.8574999999999999</v>
+      </c>
+      <c r="P778" s="9">
+        <v>3.9049999999999998</v>
+      </c>
+      <c r="Q778" s="9">
+        <v>3.9649999999999999</v>
+      </c>
+      <c r="R778" s="9">
+        <v>4.0149999999999997</v>
+      </c>
+    </row>
+    <row r="779" spans="1:18">
+      <c r="A779" s="4">
+        <v>46244</v>
+      </c>
+      <c r="B779" s="4">
+        <v>46244</v>
+      </c>
+      <c r="C779" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D779" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E779" s="2">
+        <v>3.4474999999999998</v>
+      </c>
+      <c r="F779" s="2">
+        <v>3.7174999999999998</v>
+      </c>
+      <c r="G779" s="2">
+        <v>3.8224999999999998</v>
+      </c>
+      <c r="H779" s="2">
+        <v>3.89</v>
+      </c>
+      <c r="I779" s="2">
+        <v>3.9375</v>
+      </c>
+      <c r="J779" s="2">
+        <v>3.9925000000000002</v>
+      </c>
+      <c r="K779" s="2">
+        <v>3.0425</v>
+      </c>
+      <c r="L779" s="9">
+        <v>3.4474999999999998</v>
+      </c>
+      <c r="M779" s="9">
+        <v>3.7174999999999998</v>
+      </c>
+      <c r="N779" s="9">
+        <v>3.8224999999999998</v>
+      </c>
+      <c r="O779" s="9">
+        <v>3.89</v>
+      </c>
+      <c r="P779" s="9">
+        <v>3.9375</v>
+      </c>
+      <c r="Q779" s="9">
+        <v>3.9925000000000002</v>
+      </c>
+      <c r="R779" s="9">
+        <v>4.0425000000000004</v>
+      </c>
+    </row>
+    <row r="780" spans="1:18">
+      <c r="A780" s="4">
+        <v>46245</v>
+      </c>
+      <c r="B780" s="4">
+        <v>46245</v>
+      </c>
+      <c r="C780" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D780" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E780" s="2">
+        <v>3.4674999999999998</v>
+      </c>
+      <c r="F780" s="2">
+        <v>3.7374999999999998</v>
+      </c>
+      <c r="G780" s="2">
+        <v>3.85</v>
+      </c>
+      <c r="H780" s="2">
+        <v>3.9175</v>
+      </c>
+      <c r="I780" s="2">
+        <v>3.97</v>
+      </c>
+      <c r="J780" s="2">
+        <v>4.0350000000000001</v>
+      </c>
+      <c r="K780" s="2">
+        <v>4.0949999999999998</v>
+      </c>
+      <c r="L780" s="9">
+        <v>3.4674999999999998</v>
+      </c>
+      <c r="M780" s="9">
+        <v>3.7374999999999998</v>
+      </c>
+      <c r="N780" s="9">
+        <v>3.85</v>
+      </c>
+      <c r="O780" s="9">
+        <v>3.9175</v>
+      </c>
+      <c r="P780" s="9">
+        <v>3.97</v>
+      </c>
+      <c r="Q780" s="9">
+        <v>4.0350000000000001</v>
+      </c>
+      <c r="R780" s="9">
+        <v>4.0949999999999998</v>
+      </c>
+    </row>
+    <row r="781" spans="1:18">
+      <c r="A781" s="4">
+        <v>46246</v>
+      </c>
+      <c r="B781" s="4">
+        <v>46246</v>
+      </c>
+      <c r="C781" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D781" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E781" s="2">
+        <v>3.45</v>
+      </c>
+      <c r="F781" s="2">
+        <v>3.72</v>
+      </c>
+      <c r="G781" s="2">
+        <v>3.8325</v>
+      </c>
+      <c r="H781" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="I781" s="2">
+        <v>3.95</v>
+      </c>
+      <c r="J781" s="2">
+        <v>4.0225</v>
+      </c>
+      <c r="K781" s="2">
+        <v>4.085</v>
+      </c>
+      <c r="L781" s="9">
+        <v>3.45</v>
+      </c>
+      <c r="M781" s="9">
+        <v>3.72</v>
+      </c>
+      <c r="N781" s="9">
+        <v>3.8325</v>
+      </c>
+      <c r="O781" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="P781" s="9">
+        <v>3.95</v>
+      </c>
+      <c r="Q781" s="9">
+        <v>4.0225</v>
+      </c>
+      <c r="R781" s="9">
+        <v>4.085</v>
+      </c>
+    </row>
+    <row r="782" spans="1:18">
+      <c r="A782" s="4">
+        <v>46247</v>
+      </c>
+      <c r="B782" s="4">
+        <v>46247</v>
+      </c>
+      <c r="C782" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D782" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E782" s="2">
+        <v>3.45</v>
+      </c>
+      <c r="F782" s="2">
+        <v>3.7275</v>
+      </c>
+      <c r="G782" s="2">
+        <v>3.84</v>
+      </c>
+      <c r="H782" s="2">
+        <v>3.9024999999999999</v>
+      </c>
+      <c r="I782" s="2">
+        <v>3.9550000000000001</v>
+      </c>
+      <c r="J782" s="2">
+        <v>4.0274999999999999</v>
+      </c>
+      <c r="K782" s="2">
+        <v>4.0925000000000002</v>
+      </c>
+      <c r="L782" s="9">
+        <v>3.45</v>
+      </c>
+      <c r="M782" s="9">
+        <v>3.7275</v>
+      </c>
+      <c r="N782" s="9">
+        <v>3.84</v>
+      </c>
+      <c r="O782" s="9">
+        <v>3.9024999999999999</v>
+      </c>
+      <c r="P782" s="9">
+        <v>3.9550000000000001</v>
+      </c>
+      <c r="Q782" s="9">
+        <v>4.0274999999999999</v>
+      </c>
+      <c r="R782" s="9">
+        <v>4.0925000000000002</v>
+      </c>
+    </row>
+    <row r="783" spans="1:18">
+      <c r="A783" s="4">
+        <v>46248</v>
+      </c>
+      <c r="B783" s="4">
+        <v>46248</v>
+      </c>
+      <c r="C783" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D783" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E783" s="2">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="F783" s="2">
+        <v>3.7374999999999998</v>
+      </c>
+      <c r="G783" s="2">
+        <v>3.8525</v>
+      </c>
+      <c r="H783" s="2">
+        <v>3.915</v>
+      </c>
+      <c r="I783" s="2">
+        <v>3.9674999999999998</v>
+      </c>
+      <c r="J783" s="2">
+        <v>4.03</v>
+      </c>
+      <c r="K783" s="2">
+        <v>4.085</v>
+      </c>
+      <c r="L783" s="9">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="M783" s="9">
+        <v>3.7374999999999998</v>
+      </c>
+      <c r="N783" s="9">
+        <v>3.8525</v>
+      </c>
+      <c r="O783" s="9">
+        <v>3.915</v>
+      </c>
+      <c r="P783" s="9">
+        <v>3.9674999999999998</v>
+      </c>
+      <c r="Q783" s="9">
+        <v>4.03</v>
+      </c>
+      <c r="R783" s="9">
+        <v>4.085</v>
       </c>
     </row>
   </sheetData>
@@ -43812,250 +44427,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B53C53-446E-4959-A400-CF5DFAD5C745}">
-  <dimension ref="B2:I10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="11">
-        <v>46223</v>
-      </c>
-      <c r="C2">
-        <v>3.0449999999999999</v>
-      </c>
-      <c r="D2">
-        <v>3.26</v>
-      </c>
-      <c r="E2">
-        <v>3.43</v>
-      </c>
-      <c r="F2">
-        <v>3.52</v>
-      </c>
-      <c r="G2">
-        <v>3.57</v>
-      </c>
-      <c r="H2">
-        <v>3.61</v>
-      </c>
-      <c r="I2">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="11">
-        <v>46224</v>
-      </c>
-      <c r="C3">
-        <v>3.0550000000000002</v>
-      </c>
-      <c r="D3">
-        <v>3.27</v>
-      </c>
-      <c r="E3">
-        <v>3.4350000000000001</v>
-      </c>
-      <c r="F3">
-        <v>3.5249999999999999</v>
-      </c>
-      <c r="G3">
-        <v>3.5750000000000002</v>
-      </c>
-      <c r="H3">
-        <v>3.6150000000000002</v>
-      </c>
-      <c r="I3">
-        <v>3.5249999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="11">
-        <v>46225</v>
-      </c>
-      <c r="C4">
-        <v>3.105</v>
-      </c>
-      <c r="D4">
-        <v>3.33</v>
-      </c>
-      <c r="E4">
-        <v>3.4849999999999999</v>
-      </c>
-      <c r="F4">
-        <v>3.57</v>
-      </c>
-      <c r="G4">
-        <v>3.62</v>
-      </c>
-      <c r="H4">
-        <v>3.66</v>
-      </c>
-      <c r="I4">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="11">
-        <v>46226</v>
-      </c>
-      <c r="C5">
-        <v>3.1749999999999998</v>
-      </c>
-      <c r="D5">
-        <v>3.38</v>
-      </c>
-      <c r="E5">
-        <v>3.5249999999999999</v>
-      </c>
-      <c r="F5">
-        <v>3.6</v>
-      </c>
-      <c r="G5">
-        <v>3.64</v>
-      </c>
-      <c r="H5">
-        <v>3.68</v>
-      </c>
-      <c r="I5">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="11">
-        <v>46227</v>
-      </c>
-      <c r="C6">
-        <v>3.26</v>
-      </c>
-      <c r="D6">
-        <v>3.44</v>
-      </c>
-      <c r="E6">
-        <v>3.5750000000000002</v>
-      </c>
-      <c r="F6">
-        <v>3.64</v>
-      </c>
-      <c r="G6">
-        <v>3.68</v>
-      </c>
-      <c r="H6">
-        <v>3.72</v>
-      </c>
-      <c r="I6">
-        <v>3.625</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="11">
-        <v>46230</v>
-      </c>
-      <c r="C7">
-        <v>3.2549999999999999</v>
-      </c>
-      <c r="D7">
-        <v>3.3849999999999998</v>
-      </c>
-      <c r="E7">
-        <v>3.5</v>
-      </c>
-      <c r="F7">
-        <v>3.55</v>
-      </c>
-      <c r="G7">
-        <v>3.58</v>
-      </c>
-      <c r="H7">
-        <v>3.62</v>
-      </c>
-      <c r="I7">
-        <v>3.5249999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="11">
-        <v>46231</v>
-      </c>
-      <c r="C8">
-        <v>3.2749999999999999</v>
-      </c>
-      <c r="D8">
-        <v>3.3849999999999998</v>
-      </c>
-      <c r="E8">
-        <v>3.4950000000000001</v>
-      </c>
-      <c r="F8">
-        <v>3.5449999999999999</v>
-      </c>
-      <c r="G8">
-        <v>3.5750000000000002</v>
-      </c>
-      <c r="H8">
-        <v>3.6150000000000002</v>
-      </c>
-      <c r="I8">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="11">
-        <v>46232</v>
-      </c>
-      <c r="C9">
-        <v>3.25</v>
-      </c>
-      <c r="D9">
-        <v>3.3650000000000002</v>
-      </c>
-      <c r="E9">
-        <v>3.48</v>
-      </c>
-      <c r="F9">
-        <v>3.53</v>
-      </c>
-      <c r="G9">
-        <v>3.56</v>
-      </c>
-      <c r="H9">
-        <v>3.6</v>
-      </c>
-      <c r="I9">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="11">
-        <v>46233</v>
-      </c>
-      <c r="C10">
-        <v>3.2050000000000001</v>
-      </c>
-      <c r="D10">
-        <v>3.3650000000000002</v>
-      </c>
-      <c r="E10">
-        <v>3.49</v>
-      </c>
-      <c r="F10">
-        <v>3.55</v>
-      </c>
-      <c r="G10">
-        <v>3.5950000000000002</v>
-      </c>
-      <c r="H10">
-        <v>3.6349999999999998</v>
-      </c>
-      <c r="I10">
-        <v>3.5350000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:I10">
-    <sortCondition ref="B2:B10"/>
-  </sortState>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44064,9 +44438,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F7B68C-7149-4431-8318-C6CA85CD9F67}">
   <dimension ref="B2:D4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -44077,7 +44451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4">
       <c r="C3" t="s">
         <v>4</v>
       </c>
@@ -44085,7 +44459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4">
       <c r="C4" t="s">
         <v>6</v>
       </c>

--- a/data_lake/fixed_income/South Korea/SwapRate.xlsx
+++ b/data_lake/fixed_income/South Korea/SwapRate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/fixed_income/South Korea/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/fixed_income/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41890353-5E01-154F-B03B-A91A977CF3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BAFA0B-442D-CF45-922E-5C9E3C29BF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24640" yWindow="600" windowWidth="26560" windowHeight="24900" xr2:uid="{C9C890FF-C3F2-4A9F-8865-0BB25D5A743B}"/>
+    <workbookView xWindow="18040" yWindow="780" windowWidth="17960" windowHeight="20860" xr2:uid="{C9C890FF-C3F2-4A9F-8865-0BB25D5A743B}"/>
   </bookViews>
   <sheets>
     <sheet name="KR" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="35">
   <si>
     <t>https://www.kmbco.com/kor/rate/deri_rate.do#article1</t>
   </si>
@@ -142,6 +142,30 @@
     <t>KRCRS10Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>전송일</t>
+  </si>
+  <si>
+    <t>1Y</t>
+  </si>
+  <si>
+    <t>2Y</t>
+  </si>
+  <si>
+    <t>3Y</t>
+  </si>
+  <si>
+    <t>4Y</t>
+  </si>
+  <si>
+    <t>5Y</t>
+  </si>
+  <si>
+    <t>7Y</t>
+  </si>
+  <si>
+    <t>10Y</t>
+  </si>
 </sst>
 </file>
 
@@ -155,7 +179,7 @@
     <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +218,25 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -220,7 +263,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -242,6 +285,9 @@
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -559,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4AAE20-6E9C-4CCD-99FF-CD3680691C67}">
-  <dimension ref="A1:R783"/>
+  <dimension ref="A1:R794"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" style="4" bestFit="1" customWidth="1"/>
@@ -44419,6 +44465,622 @@
         <v>4.085</v>
       </c>
     </row>
+    <row r="784" spans="1:18">
+      <c r="A784" s="4">
+        <v>46252</v>
+      </c>
+      <c r="B784" s="4">
+        <v>46252</v>
+      </c>
+      <c r="C784" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D784" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E784" s="2">
+        <v>3.4725000000000001</v>
+      </c>
+      <c r="F784" s="2">
+        <v>3.7650000000000001</v>
+      </c>
+      <c r="G784" s="2">
+        <v>3.8875000000000002</v>
+      </c>
+      <c r="H784" s="2">
+        <v>3.9575</v>
+      </c>
+      <c r="I784" s="2">
+        <v>4.0149999999999997</v>
+      </c>
+      <c r="J784" s="2">
+        <v>4.085</v>
+      </c>
+      <c r="K784" s="2">
+        <v>4.1475</v>
+      </c>
+      <c r="L784" s="9">
+        <v>3.4725000000000001</v>
+      </c>
+      <c r="M784" s="9">
+        <v>3.7650000000000001</v>
+      </c>
+      <c r="N784" s="9">
+        <v>3.8875000000000002</v>
+      </c>
+      <c r="O784" s="9">
+        <v>3.9575</v>
+      </c>
+      <c r="P784" s="9">
+        <v>4.0149999999999997</v>
+      </c>
+      <c r="Q784" s="9">
+        <v>4.085</v>
+      </c>
+      <c r="R784" s="9">
+        <v>4.1475</v>
+      </c>
+    </row>
+    <row r="785" spans="1:18">
+      <c r="A785" s="4">
+        <v>46253</v>
+      </c>
+      <c r="B785" s="4">
+        <v>46253</v>
+      </c>
+      <c r="C785" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D785" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E785" s="2">
+        <v>3.44</v>
+      </c>
+      <c r="F785" s="2">
+        <v>3.71</v>
+      </c>
+      <c r="G785" s="2">
+        <v>3.8325</v>
+      </c>
+      <c r="H785" s="2">
+        <v>3.9049999999999998</v>
+      </c>
+      <c r="I785" s="2">
+        <v>3.9624999999999999</v>
+      </c>
+      <c r="J785" s="2">
+        <v>4.04</v>
+      </c>
+      <c r="K785" s="2">
+        <v>4.1050000000000004</v>
+      </c>
+      <c r="L785" s="9">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="M785" s="9">
+        <v>3.395</v>
+      </c>
+      <c r="N785" s="9">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="O785" s="9">
+        <v>3.56</v>
+      </c>
+      <c r="P785" s="9">
+        <v>3.5950000000000002</v>
+      </c>
+      <c r="Q785" s="9">
+        <v>3.64</v>
+      </c>
+      <c r="R785" s="9">
+        <v>3.5350000000000001</v>
+      </c>
+    </row>
+    <row r="786" spans="1:18">
+      <c r="A786" s="4">
+        <v>46254</v>
+      </c>
+      <c r="B786" s="4">
+        <v>46254</v>
+      </c>
+      <c r="C786" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D786" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E786" s="2">
+        <v>3.46</v>
+      </c>
+      <c r="F786" s="2">
+        <v>3.74</v>
+      </c>
+      <c r="G786" s="2">
+        <v>3.8525</v>
+      </c>
+      <c r="H786" s="2">
+        <v>3.915</v>
+      </c>
+      <c r="I786" s="2">
+        <v>3.9649999999999999</v>
+      </c>
+      <c r="J786" s="2">
+        <v>4.0324999999999998</v>
+      </c>
+      <c r="K786" s="2">
+        <v>4.0975000000000001</v>
+      </c>
+      <c r="L786" s="9">
+        <v>3.27</v>
+      </c>
+      <c r="M786" s="9">
+        <v>3.415</v>
+      </c>
+      <c r="N786" s="9">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="O786" s="9">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="P786" s="9">
+        <v>3.605</v>
+      </c>
+      <c r="Q786" s="9">
+        <v>3.6549999999999998</v>
+      </c>
+      <c r="R786" s="9">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="787" spans="1:18">
+      <c r="A787" s="4">
+        <v>46255</v>
+      </c>
+      <c r="B787" s="4">
+        <v>46255</v>
+      </c>
+      <c r="C787" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D787" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E787" s="2">
+        <v>3.4624999999999999</v>
+      </c>
+      <c r="F787" s="2">
+        <v>3.7549999999999999</v>
+      </c>
+      <c r="G787" s="2">
+        <v>3.88</v>
+      </c>
+      <c r="H787" s="2">
+        <v>3.95</v>
+      </c>
+      <c r="I787" s="2">
+        <v>4.0049999999999999</v>
+      </c>
+      <c r="J787" s="2">
+        <v>4.0824999999999996</v>
+      </c>
+      <c r="K787" s="2">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="L787" s="9">
+        <v>3.29</v>
+      </c>
+      <c r="M787" s="9">
+        <v>3.4350000000000001</v>
+      </c>
+      <c r="N787" s="9">
+        <v>3.54</v>
+      </c>
+      <c r="O787" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="P787" s="9">
+        <v>3.625</v>
+      </c>
+      <c r="Q787" s="9">
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="R787" s="9">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="788" spans="1:18">
+      <c r="A788" s="4">
+        <v>46258</v>
+      </c>
+      <c r="B788" s="4">
+        <v>46258</v>
+      </c>
+      <c r="C788" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D788" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E788" s="2">
+        <v>3.4249999999999998</v>
+      </c>
+      <c r="F788" s="2">
+        <v>3.72</v>
+      </c>
+      <c r="G788" s="2">
+        <v>3.8450000000000002</v>
+      </c>
+      <c r="H788" s="2">
+        <v>3.9125000000000001</v>
+      </c>
+      <c r="I788" s="2">
+        <v>3.9624999999999999</v>
+      </c>
+      <c r="J788" s="2">
+        <v>4.04</v>
+      </c>
+      <c r="K788" s="2">
+        <v>4.1074999999999999</v>
+      </c>
+      <c r="L788" s="9">
+        <v>3.3149999999999999</v>
+      </c>
+      <c r="M788" s="9">
+        <v>3.42</v>
+      </c>
+      <c r="N788" s="9">
+        <v>3.52</v>
+      </c>
+      <c r="O788" s="9">
+        <v>3.58</v>
+      </c>
+      <c r="P788" s="9">
+        <v>3.605</v>
+      </c>
+      <c r="Q788" s="9">
+        <v>3.6549999999999998</v>
+      </c>
+      <c r="R788" s="9">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="789" spans="1:18">
+      <c r="A789" s="4">
+        <v>46259</v>
+      </c>
+      <c r="B789" s="4">
+        <v>46259</v>
+      </c>
+      <c r="C789" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D789" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E789" s="2">
+        <v>3.415</v>
+      </c>
+      <c r="F789" s="2">
+        <v>3.69</v>
+      </c>
+      <c r="G789" s="2">
+        <v>3.82</v>
+      </c>
+      <c r="H789" s="2">
+        <v>3.89</v>
+      </c>
+      <c r="I789" s="2">
+        <v>3.9424999999999999</v>
+      </c>
+      <c r="J789" s="2">
+        <v>4.0175000000000001</v>
+      </c>
+      <c r="K789" s="2">
+        <v>4.085</v>
+      </c>
+      <c r="L789" s="9">
+        <v>3.3050000000000002</v>
+      </c>
+      <c r="M789" s="9">
+        <v>3.41</v>
+      </c>
+      <c r="N789" s="9">
+        <v>3.5049999999999999</v>
+      </c>
+      <c r="O789" s="9">
+        <v>3.56</v>
+      </c>
+      <c r="P789" s="9">
+        <v>3.58</v>
+      </c>
+      <c r="Q789" s="9">
+        <v>3.625</v>
+      </c>
+      <c r="R789" s="9">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="790" spans="1:18">
+      <c r="A790" s="4">
+        <v>46260</v>
+      </c>
+      <c r="B790" s="4">
+        <v>46260</v>
+      </c>
+      <c r="C790" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D790" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E790" s="2">
+        <v>3.4325000000000001</v>
+      </c>
+      <c r="F790" s="2">
+        <v>3.7050000000000001</v>
+      </c>
+      <c r="G790" s="2">
+        <v>3.81</v>
+      </c>
+      <c r="H790" s="2">
+        <v>3.88</v>
+      </c>
+      <c r="I790" s="2">
+        <v>3.93</v>
+      </c>
+      <c r="J790" s="2">
+        <v>4</v>
+      </c>
+      <c r="K790" s="2">
+        <v>4.0625</v>
+      </c>
+      <c r="L790" s="9">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="M790" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="N790" s="9">
+        <v>3.51</v>
+      </c>
+      <c r="O790" s="9">
+        <v>3.57</v>
+      </c>
+      <c r="P790" s="9">
+        <v>3.585</v>
+      </c>
+      <c r="Q790" s="9">
+        <v>3.625</v>
+      </c>
+      <c r="R790" s="9">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="791" spans="1:18">
+      <c r="A791" s="4">
+        <v>46261</v>
+      </c>
+      <c r="B791" s="4">
+        <v>46261</v>
+      </c>
+      <c r="C791" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D791" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E791" s="2">
+        <v>3.4449999999999998</v>
+      </c>
+      <c r="F791" s="2">
+        <v>3.6575000000000002</v>
+      </c>
+      <c r="G791" s="2">
+        <v>3.7549999999999999</v>
+      </c>
+      <c r="H791" s="2">
+        <v>3.83</v>
+      </c>
+      <c r="I791" s="2">
+        <v>3.875</v>
+      </c>
+      <c r="J791" s="2">
+        <v>3.9449999999999998</v>
+      </c>
+      <c r="K791" s="2">
+        <v>4.0049999999999999</v>
+      </c>
+      <c r="L791" s="9">
+        <v>3.415</v>
+      </c>
+      <c r="M791" s="9">
+        <v>3.415</v>
+      </c>
+      <c r="N791" s="9">
+        <v>3.4849999999999999</v>
+      </c>
+      <c r="O791" s="9">
+        <v>3.5350000000000001</v>
+      </c>
+      <c r="P791" s="9">
+        <v>3.55</v>
+      </c>
+      <c r="Q791" s="9">
+        <v>3.59</v>
+      </c>
+      <c r="R791" s="9">
+        <v>3.4849999999999999</v>
+      </c>
+    </row>
+    <row r="792" spans="1:18">
+      <c r="A792" s="4">
+        <v>46262</v>
+      </c>
+      <c r="B792" s="4">
+        <v>46262</v>
+      </c>
+      <c r="C792" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D792" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E792" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="F792" s="2">
+        <v>3.7174999999999998</v>
+      </c>
+      <c r="G792" s="2">
+        <v>3.8174999999999999</v>
+      </c>
+      <c r="H792" s="2">
+        <v>3.8875000000000002</v>
+      </c>
+      <c r="I792" s="2">
+        <v>3.9375</v>
+      </c>
+      <c r="J792" s="2">
+        <v>4.0049999999999999</v>
+      </c>
+      <c r="K792" s="2">
+        <v>4.0625</v>
+      </c>
+      <c r="L792" s="9">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="M792" s="9">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="N792" s="9">
+        <v>3.53</v>
+      </c>
+      <c r="O792" s="9">
+        <v>3.57</v>
+      </c>
+      <c r="P792" s="9">
+        <v>3.585</v>
+      </c>
+      <c r="Q792" s="9">
+        <v>3.625</v>
+      </c>
+      <c r="R792" s="9">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="793" spans="1:18">
+      <c r="A793" s="4">
+        <v>46265</v>
+      </c>
+      <c r="B793" s="4">
+        <v>46265</v>
+      </c>
+      <c r="C793" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D793" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E793" s="2">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="F793" s="2">
+        <v>3.76</v>
+      </c>
+      <c r="G793" s="2">
+        <v>3.86</v>
+      </c>
+      <c r="H793" s="2">
+        <v>3.9275000000000002</v>
+      </c>
+      <c r="I793" s="2">
+        <v>3.9725000000000001</v>
+      </c>
+      <c r="J793" s="2">
+        <v>4.0324999999999998</v>
+      </c>
+      <c r="K793" s="2">
+        <v>4.0824999999999996</v>
+      </c>
+      <c r="L793" s="9">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="M793" s="9">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="N793" s="9">
+        <v>3.5550000000000002</v>
+      </c>
+      <c r="O793" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="P793" s="9">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="Q793" s="9">
+        <v>3.6549999999999998</v>
+      </c>
+      <c r="R793" s="9">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="794" spans="1:18">
+      <c r="A794" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B794" s="4">
+        <v>46266</v>
+      </c>
+      <c r="C794" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="D794" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E794" s="2">
+        <v>3.5375000000000001</v>
+      </c>
+      <c r="F794" s="2">
+        <v>3.7825000000000002</v>
+      </c>
+      <c r="G794" s="2">
+        <v>3.8925000000000001</v>
+      </c>
+      <c r="H794" s="2">
+        <v>3.96</v>
+      </c>
+      <c r="I794" s="2">
+        <v>4.0049999999999999</v>
+      </c>
+      <c r="J794" s="2">
+        <v>4.07</v>
+      </c>
+      <c r="K794" s="2">
+        <v>4.13</v>
+      </c>
+      <c r="L794" s="9">
+        <v>3.52</v>
+      </c>
+      <c r="M794" s="9">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="N794" s="9">
+        <v>3.59</v>
+      </c>
+      <c r="O794" s="9">
+        <v>3.6349999999999998</v>
+      </c>
+      <c r="P794" s="9">
+        <v>3.65</v>
+      </c>
+      <c r="Q794" s="9">
+        <v>3.69</v>
+      </c>
+      <c r="R794" s="9">
+        <v>3.585</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44427,9 +45089,328 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B53C53-446E-4959-A400-CF5DFAD5C745}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:I13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="23">
+      <c r="B2" s="11">
+        <v>46252</v>
+      </c>
+      <c r="C2" s="12">
+        <v>3.4725000000000001</v>
+      </c>
+      <c r="D2" s="12">
+        <v>3.7650000000000001</v>
+      </c>
+      <c r="E2" s="12">
+        <v>3.8875000000000002</v>
+      </c>
+      <c r="F2" s="12">
+        <v>3.9575</v>
+      </c>
+      <c r="G2" s="12">
+        <v>4.0149999999999997</v>
+      </c>
+      <c r="H2" s="12">
+        <v>4.085</v>
+      </c>
+      <c r="I2" s="12">
+        <v>4.1475</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="23">
+      <c r="B3" s="11">
+        <v>46253</v>
+      </c>
+      <c r="C3" s="12">
+        <v>3.2650000000000001</v>
+      </c>
+      <c r="D3" s="12">
+        <v>3.395</v>
+      </c>
+      <c r="E3" s="12">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="F3" s="12">
+        <v>3.56</v>
+      </c>
+      <c r="G3" s="12">
+        <v>3.5950000000000002</v>
+      </c>
+      <c r="H3" s="12">
+        <v>3.64</v>
+      </c>
+      <c r="I3" s="12">
+        <v>3.5350000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="23">
+      <c r="B4" s="11">
+        <v>46254</v>
+      </c>
+      <c r="C4" s="12">
+        <v>3.27</v>
+      </c>
+      <c r="D4" s="12">
+        <v>3.415</v>
+      </c>
+      <c r="E4" s="12">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="F4" s="12">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="G4" s="12">
+        <v>3.605</v>
+      </c>
+      <c r="H4" s="12">
+        <v>3.6549999999999998</v>
+      </c>
+      <c r="I4" s="12">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="23">
+      <c r="B5" s="11">
+        <v>46255</v>
+      </c>
+      <c r="C5" s="12">
+        <v>3.29</v>
+      </c>
+      <c r="D5" s="12">
+        <v>3.4350000000000001</v>
+      </c>
+      <c r="E5" s="12">
+        <v>3.54</v>
+      </c>
+      <c r="F5" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G5" s="12">
+        <v>3.625</v>
+      </c>
+      <c r="H5" s="12">
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="I5" s="12">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="23">
+      <c r="B6" s="11">
+        <v>46258</v>
+      </c>
+      <c r="C6" s="12">
+        <v>3.3149999999999999</v>
+      </c>
+      <c r="D6" s="12">
+        <v>3.42</v>
+      </c>
+      <c r="E6" s="12">
+        <v>3.52</v>
+      </c>
+      <c r="F6" s="12">
+        <v>3.58</v>
+      </c>
+      <c r="G6" s="12">
+        <v>3.605</v>
+      </c>
+      <c r="H6" s="12">
+        <v>3.6549999999999998</v>
+      </c>
+      <c r="I6" s="12">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="23">
+      <c r="B7" s="11">
+        <v>46259</v>
+      </c>
+      <c r="C7" s="12">
+        <v>3.3050000000000002</v>
+      </c>
+      <c r="D7" s="12">
+        <v>3.41</v>
+      </c>
+      <c r="E7" s="12">
+        <v>3.5049999999999999</v>
+      </c>
+      <c r="F7" s="12">
+        <v>3.56</v>
+      </c>
+      <c r="G7" s="12">
+        <v>3.58</v>
+      </c>
+      <c r="H7" s="12">
+        <v>3.625</v>
+      </c>
+      <c r="I7" s="12">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="23">
+      <c r="B8" s="11">
+        <v>46260</v>
+      </c>
+      <c r="C8" s="12">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="D8" s="12">
+        <v>3.43</v>
+      </c>
+      <c r="E8" s="12">
+        <v>3.51</v>
+      </c>
+      <c r="F8" s="12">
+        <v>3.57</v>
+      </c>
+      <c r="G8" s="12">
+        <v>3.585</v>
+      </c>
+      <c r="H8" s="12">
+        <v>3.625</v>
+      </c>
+      <c r="I8" s="12">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="23">
+      <c r="B9" s="11">
+        <v>46261</v>
+      </c>
+      <c r="C9" s="12">
+        <v>3.415</v>
+      </c>
+      <c r="D9" s="12">
+        <v>3.415</v>
+      </c>
+      <c r="E9" s="12">
+        <v>3.4849999999999999</v>
+      </c>
+      <c r="F9" s="12">
+        <v>3.5350000000000001</v>
+      </c>
+      <c r="G9" s="12">
+        <v>3.55</v>
+      </c>
+      <c r="H9" s="12">
+        <v>3.59</v>
+      </c>
+      <c r="I9" s="12">
+        <v>3.4849999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="23">
+      <c r="B10" s="11">
+        <v>46262</v>
+      </c>
+      <c r="C10" s="12">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="D10" s="12">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="E10" s="12">
+        <v>3.53</v>
+      </c>
+      <c r="F10" s="12">
+        <v>3.57</v>
+      </c>
+      <c r="G10" s="12">
+        <v>3.585</v>
+      </c>
+      <c r="H10" s="12">
+        <v>3.625</v>
+      </c>
+      <c r="I10" s="12">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="23">
+      <c r="B11" s="11">
+        <v>46265</v>
+      </c>
+      <c r="C11" s="12">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="D11" s="12">
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="E11" s="12">
+        <v>3.5550000000000002</v>
+      </c>
+      <c r="F11" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G11" s="12">
+        <v>3.6150000000000002</v>
+      </c>
+      <c r="H11" s="12">
+        <v>3.6549999999999998</v>
+      </c>
+      <c r="I11" s="12">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="23">
+      <c r="B12" s="11">
+        <v>46266</v>
+      </c>
+      <c r="C12" s="12">
+        <v>3.52</v>
+      </c>
+      <c r="D12" s="12">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="E12" s="12">
+        <v>3.59</v>
+      </c>
+      <c r="F12" s="12">
+        <v>3.6349999999999998</v>
+      </c>
+      <c r="G12" s="12">
+        <v>3.65</v>
+      </c>
+      <c r="H12" s="12">
+        <v>3.69</v>
+      </c>
+      <c r="I12" s="12">
+        <v>3.585</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="23">
+      <c r="B13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:I13">
+    <sortCondition ref="B2:B13"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
